--- a/.claude/skills/sycebnl/liasse/assets/gabarit-etats-associations.xlsx
+++ b/.claude/skills/sycebnl/liasse/assets/gabarit-etats-associations.xlsx
@@ -79,7 +79,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0\ _€_-;\-* #,##0\ _€_-;_-* &quot;-&quot;\ _€_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -218,6 +218,12 @@
       <b val="1"/>
       <color rgb="00D9D9D9"/>
       <sz val="26"/>
+    </font>
+    <font>
+      <name val="Arial Black"/>
+      <b val="1"/>
+      <color rgb="00D9D9D9"/>
+      <sz val="48"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -656,7 +662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -942,8 +948,11 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="15"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1963,11 +1972,11 @@
         </is>
       </c>
       <c r="D25" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2080,11 +2089,11 @@
         </is>
       </c>
       <c r="D30" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2155,11 +2164,11 @@
         </is>
       </c>
       <c r="D33" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"599*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"499*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"479*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"599*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"499*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"479*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"599*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"499*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"479*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"599*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"499*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"479*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000))</f>
         <v/>
       </c>
     </row>
@@ -2585,11 +2594,11 @@
         </is>
       </c>
       <c r="D16" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E16" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2731,11 +2740,11 @@
         </is>
       </c>
       <c r="D22" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E22" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2756,11 +2765,11 @@
         </is>
       </c>
       <c r="D23" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E23" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2806,11 +2815,11 @@
         </is>
       </c>
       <c r="D25" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"62*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"62*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"63*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"63*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"63*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"63*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"62*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"62*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"62*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"62*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"63*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"63*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"63*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"63*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"62*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"62*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2931,11 +2940,11 @@
         </is>
       </c>
       <c r="D30" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2998,11 +3007,11 @@
         </is>
       </c>
       <c r="D33" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -3023,11 +3032,11 @@
         </is>
       </c>
       <c r="D34" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E34" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -3217,7 +3226,7 @@
         </is>
       </c>
       <c r="D9" s="101">
-        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)))))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$G$2:$G$2000))+(SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)))))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$G$2:$G$2000))+(SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E9" s="102" t="n"/>
@@ -3463,7 +3472,7 @@
         </is>
       </c>
       <c r="D25" s="84">
-        <f>-((((SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$H$2:$H$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$H$2:$H$2000)))))</f>
+        <f>-((((SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$H$2:$H$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$H$2:$H$2000)))))</f>
         <v/>
       </c>
       <c r="E25" s="85" t="n"/>
@@ -3604,7 +3613,7 @@
         </is>
       </c>
       <c r="D34" s="7">
-        <f>(((SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$G$2:$G$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$G$2:$G$2000))))</f>
+        <f>(((SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$G$2:$G$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$G$2:$G$2000))))</f>
         <v/>
       </c>
       <c r="E34" s="82" t="n"/>
@@ -3626,7 +3635,7 @@
         </is>
       </c>
       <c r="D35" s="101">
-        <f>(((((SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)))))-((SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$G$2:$G$2000))+(SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000))))-D9</f>
+        <f>(((((SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)))))-((SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$G$2:$G$2000))+(SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000))))-D9</f>
         <v/>
       </c>
       <c r="E35" s="102" t="n"/>
@@ -5027,7 +5036,7 @@
       </c>
       <c r="B13" s="119" t="inlineStr"/>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D13" s="120" t="n"/>
@@ -5088,7 +5097,7 @@
       </c>
       <c r="B17" s="119" t="inlineStr"/>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
@@ -5467,14 +5476,14 @@
       </c>
     </row>
     <row r="47"/>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="114">
-        <f>IF(SUM(B33:B44,C10:C44,D10:D36,E10:E26,F10:F26)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="26" customHeight="1"/>
-    <row r="50" ht="26" customHeight="1"/>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="122">
+        <f>IF(SUM(B33:B44,C10:C44,D10:D36,E10:E26,F10:F26)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1"/>
+    <row r="50" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="E2:F2"/>
@@ -5574,7 +5583,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>A - IDENTITÉ, ORGANISATION : décrire brièvement l'identité de l'entité (date de création, nature du projet associatif, mission) et l'organisation avec des données chiffrées (effectifs, nombre de bénévoles, total des revenus, moyens utilisés).</t>
         </is>
@@ -5583,7 +5592,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>B - DÉCLARATION DE CONFORMITÉ AU SYSTÈME COMPTABLE DES ENTITÉS À BUT NON LUCRATIF ET FAITS MARQUANTS DE L'EXERCICE.</t>
         </is>
@@ -5592,7 +5601,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>C - RÈGLES, MÉTHODES COMPTABLES ET DÉROGATION AUX PRINCIPES COMPTABLES.</t>
         </is>
@@ -5601,7 +5610,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>D - INFORMATIONS COMPLÉMENTAIRES RELATIVES AU BILAN, AU COMPTE DE RÉSULTAT ET AU TABLEAU DES FLUX DE TRÉSORERIE.</t>
         </is>
@@ -5721,7 +5730,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Date d'arrêté des états financiers : </t>
         </is>
@@ -5730,7 +5739,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Organe ayant autorisé la publication des comptes : </t>
         </is>
@@ -5739,7 +5748,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>A - ÉVÈNEMENTS POSTÉRIEURS DONNANT LIEU À AJUSTEMENTS : nature des évènements et précisions sur les comptes ajustés.</t>
         </is>
@@ -5748,7 +5757,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>B - ÉVÈNEMENTS POSTÉRIEURS NE DONNANT PAS LIEU À AJUSTEMENTS : estimation de l'impact financier ou indication que l'estimation ne peut être fournie.</t>
         </is>
@@ -5757,7 +5766,7 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="122" t="inlineStr">
+      <c r="A21" s="123" t="inlineStr">
         <is>
           <t>C - ÉVÈNEMENTS REMETTANT EN CAUSE LA CONTINUITÉ DE L'EXPLOITATION : nature de l'évènement, valeurs liquidatives retenues.</t>
         </is>
@@ -5878,7 +5887,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>A - CHANGEMENTS DE MÉTHODES COMPTABLES : 1. changement de réglementation comptable ; 2. changement à l'initiative de l'entité (impact à l'ouverture, retraitement rétrospectif ou application prospective).</t>
         </is>
@@ -5887,7 +5896,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>B - CHANGEMENTS D'ESTIMATIONS : indiquer et justifier le changement d'estimation.</t>
         </is>
@@ -5896,7 +5905,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>C - CORRECTIONS D'ERREURS : nature des erreurs corrigées et principaux postes retraités.</t>
         </is>
@@ -6039,15 +6048,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS INCORPORELLES</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="124" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="125" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -6119,15 +6128,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="123" t="inlineStr">
+      <c r="A13" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS CORPORELLES</t>
         </is>
       </c>
-      <c r="B13" s="124" t="n"/>
-      <c r="C13" s="124" t="n"/>
-      <c r="D13" s="124" t="n"/>
-      <c r="E13" s="124" t="n"/>
+      <c r="B13" s="125" t="n"/>
+      <c r="C13" s="125" t="n"/>
+      <c r="D13" s="125" t="n"/>
+      <c r="E13" s="125" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="119" t="inlineStr">
@@ -6199,15 +6208,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="123" t="inlineStr">
+      <c r="A17" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS FINANCIÈRES</t>
         </is>
       </c>
-      <c r="B17" s="124" t="n"/>
-      <c r="C17" s="124" t="n"/>
-      <c r="D17" s="124" t="n"/>
-      <c r="E17" s="124" t="n"/>
+      <c r="B17" s="125" t="n"/>
+      <c r="C17" s="125" t="n"/>
+      <c r="D17" s="125" t="n"/>
+      <c r="E17" s="125" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="119" t="inlineStr">
@@ -6264,14 +6273,14 @@
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19,E9:E19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19,E9:E19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -6394,15 +6403,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS INCORPORELLES</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="124" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="125" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -6411,15 +6420,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -6497,15 +6506,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="123" t="inlineStr">
+      <c r="A14" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS CORPORELLES</t>
         </is>
       </c>
-      <c r="B14" s="124" t="n"/>
-      <c r="C14" s="124" t="n"/>
-      <c r="D14" s="124" t="n"/>
-      <c r="E14" s="124" t="n"/>
+      <c r="B14" s="125" t="n"/>
+      <c r="C14" s="125" t="n"/>
+      <c r="D14" s="125" t="n"/>
+      <c r="E14" s="125" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="119" t="inlineStr">
@@ -6560,15 +6569,15 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E17" s="120">
@@ -6692,15 +6701,15 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="123" t="inlineStr">
+      <c r="A23" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS FINANCIÈRES</t>
         </is>
       </c>
-      <c r="B23" s="124" t="n"/>
-      <c r="C23" s="124" t="n"/>
-      <c r="D23" s="124" t="n"/>
-      <c r="E23" s="124" t="n"/>
+      <c r="B23" s="125" t="n"/>
+      <c r="C23" s="125" t="n"/>
+      <c r="D23" s="125" t="n"/>
+      <c r="E23" s="125" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="119" t="inlineStr">
@@ -6780,14 +6789,14 @@
       </c>
     </row>
     <row r="29"/>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="114">
-        <f>IF(SUM(B9:B26,C9:C26,D9:D26,E9:E26)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1"/>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="122">
+        <f>IF(SUM(B9:B26,C9:C26,D9:D26,E9:E26)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1"/>
+    <row r="32" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -6998,7 +7007,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="125" t="inlineStr">
+      <c r="A8" s="126" t="inlineStr">
         <is>
           <t>I : crédit-bail immobilier ; M : crédit-bail mobilier ; A : autres contrats</t>
         </is>
@@ -7084,15 +7093,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -7155,14 +7164,14 @@
       </c>
     </row>
     <row r="17"/>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="114">
-        <f>IF(SUM(B10:B14,C10:C14,D10:D14,E10:E14)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1"/>
-    <row r="20" ht="26" customHeight="1"/>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="122">
+        <f>IF(SUM(B10:B14,C10:C14,D10:D14,E10:E14)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A8:E8"/>
@@ -7363,14 +7372,14 @@
       </c>
     </row>
     <row r="14"/>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="114">
-        <f>IF(SUM(B9:B11,C9:C11,D9:D11,E9:E11)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1"/>
-    <row r="17" ht="26" customHeight="1"/>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="122">
+        <f>IF(SUM(B9:B11,C9:C11,D9:D11,E9:E11)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A15:E17"/>
@@ -7493,15 +7502,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS INCORPORELLES</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="124" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="125" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -7510,15 +7519,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -7573,15 +7582,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="123" t="inlineStr">
+      <c r="A13" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS CORPORELLES</t>
         </is>
       </c>
-      <c r="B13" s="124" t="n"/>
-      <c r="C13" s="124" t="n"/>
-      <c r="D13" s="124" t="n"/>
-      <c r="E13" s="124" t="n"/>
+      <c r="B13" s="125" t="n"/>
+      <c r="C13" s="125" t="n"/>
+      <c r="D13" s="125" t="n"/>
+      <c r="E13" s="125" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="119" t="inlineStr">
@@ -7613,15 +7622,15 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="E15" s="120">
@@ -7636,15 +7645,15 @@
         </is>
       </c>
       <c r="B16" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="E16" s="120">
@@ -7730,14 +7739,14 @@
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19,E9:E19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19,E9:E19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -7860,15 +7869,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS INCORPORELLES</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="124" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="125" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -7894,15 +7903,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="123" t="inlineStr">
+      <c r="A11" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS CORPORELLES</t>
         </is>
       </c>
-      <c r="B11" s="124" t="n"/>
-      <c r="C11" s="124" t="n"/>
-      <c r="D11" s="124" t="n"/>
-      <c r="E11" s="124" t="n"/>
+      <c r="B11" s="125" t="n"/>
+      <c r="C11" s="125" t="n"/>
+      <c r="D11" s="125" t="n"/>
+      <c r="E11" s="125" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="119" t="inlineStr">
@@ -8020,15 +8029,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="123" t="inlineStr">
+      <c r="A17" s="124" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS FINANCIÈRES</t>
         </is>
       </c>
-      <c r="B17" s="124" t="n"/>
-      <c r="C17" s="124" t="n"/>
-      <c r="D17" s="124" t="n"/>
-      <c r="E17" s="124" t="n"/>
+      <c r="B17" s="125" t="n"/>
+      <c r="C17" s="125" t="n"/>
+      <c r="D17" s="125" t="n"/>
+      <c r="E17" s="125" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="119" t="inlineStr">
@@ -8108,14 +8117,14 @@
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="114">
-        <f>IF(SUM(B9:B20,C9:C20,D9:D20,E9:E20)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="122">
+        <f>IF(SUM(B9:B20,C9:C20,D9:D20,E9:E20)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -8364,14 +8373,14 @@
       </c>
     </row>
     <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="114">
-        <f>IF(SUM(B9:B13,C9:C13,D9:D13,E9:E13,F9:F13)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1"/>
-    <row r="19" ht="26" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="122">
+        <f>IF(SUM(B9:B13,C9:C13,D9:D13,E9:E13,F9:F13)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A17:F19"/>
@@ -8471,7 +8480,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nature et date des réévaluations : </t>
         </is>
@@ -8480,7 +8489,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>Éléments réévalués par postes du bilan | Montants en coûts historiques | Montants réévalués | Écarts et provisions spéciales de réévaluation.</t>
         </is>
@@ -8489,7 +8498,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Méthode de réévaluation utilisée : </t>
         </is>
@@ -8498,7 +8507,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Traitement fiscal de l'écart de réévaluation et des amortissements supplémentaires : </t>
         </is>
@@ -8507,7 +8516,7 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="122" t="inlineStr">
+      <c r="A21" s="123" t="inlineStr">
         <is>
           <t xml:space="preserve">Montant de l'écart incorporé à la dotation : </t>
         </is>
@@ -8690,7 +8699,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -8705,18 +8714,18 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"278*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"278*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"271*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"271*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"271*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"271*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"278*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"278*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"278*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"278*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"271*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"271*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"271*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"271*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"278*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"278*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D10" s="120">
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -8742,7 +8751,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -8768,7 +8777,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -8794,7 +8803,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -8820,7 +8829,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -8846,7 +8855,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -8872,7 +8881,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -8898,7 +8907,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -8924,7 +8933,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -8946,7 +8955,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -8972,7 +8981,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="128">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -8989,21 +8998,21 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="122" t="inlineStr">
+      <c r="A23" s="123" t="inlineStr">
         <is>
           <t>• Justifier toute variation significative ; commenter les créances anciennes ; indiquer le nombre et la date d'acquisition des actions ou parts ; pour les dépréciations, indiquer les évènements et circonstances.</t>
         </is>
       </c>
     </row>
     <row r="24"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="114">
-        <f>IF(SUM(B9:B20,C9:C20,D9:D20,F16:F20,G16:G20,H16:H20)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1"/>
-    <row r="27" ht="26" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="122">
+        <f>IF(SUM(B9:B20,C9:C20,D9:D20,F16:F20,G16:G20,H16:H20)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -9130,15 +9139,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>ACTIF CIRCULANT HAO</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="128" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="129" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -9158,7 +9167,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -9181,7 +9190,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -9204,7 +9213,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="128">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -9227,7 +9236,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -9246,7 +9255,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -9269,7 +9278,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -9282,15 +9291,15 @@
       <c r="E16" s="119" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="123" t="inlineStr">
+      <c r="A17" s="124" t="inlineStr">
         <is>
           <t>DETTES CIRCULANTES HAO</t>
         </is>
       </c>
-      <c r="B17" s="124" t="n"/>
-      <c r="C17" s="124" t="n"/>
-      <c r="D17" s="124" t="n"/>
-      <c r="E17" s="128" t="n"/>
+      <c r="B17" s="125" t="n"/>
+      <c r="C17" s="125" t="n"/>
+      <c r="D17" s="125" t="n"/>
+      <c r="E17" s="129" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="119" t="inlineStr">
@@ -9310,7 +9319,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -9333,7 +9342,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -9356,7 +9365,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -9368,18 +9377,18 @@
         </is>
       </c>
       <c r="B21" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4881*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4881*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4881*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4881*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C21" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4881*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4881*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4881*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4881*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D21" s="120">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -9402,7 +9411,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="127">
+      <c r="E22" s="128">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -9416,21 +9425,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>• Commenter toute variation significative ; indiquer la date et la nature de l'immobilisation achetée et/ou cédée.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B22,C9:C22,D9:D22)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B22,C9:C22,D9:D22)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -9573,7 +9582,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -9596,7 +9605,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -9619,7 +9628,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -9642,7 +9651,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -9654,18 +9663,18 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"35*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"35*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"35*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"35*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"35*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"35*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"35*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"35*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D13" s="120">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -9688,7 +9697,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -9711,7 +9720,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -9734,7 +9743,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -9757,7 +9766,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -9776,7 +9785,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -9799,7 +9808,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -9813,21 +9822,21 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="122" t="inlineStr">
+      <c r="A22" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la date de prise d'inventaire, la procédure et les méthodes d'évaluation ; commenter toute variation significative ; détailler les stocks dépréciés.</t>
         </is>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -9988,7 +9997,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -10014,7 +10023,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -10040,7 +10049,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -10066,7 +10075,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -10092,7 +10101,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -10118,7 +10127,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -10144,7 +10153,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -10166,7 +10175,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -10192,7 +10201,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -10228,7 +10237,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -10254,7 +10263,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -10269,18 +10278,18 @@
         </is>
       </c>
       <c r="B21" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"419*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4192*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4191*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"419*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4191*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4192*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C21" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"419*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4192*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4191*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"419*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4191*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4192*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D21" s="120">
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -10306,7 +10315,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="127">
+      <c r="E22" s="128">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -10323,21 +10332,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>• Commenter toute variation significative et les créances anciennes ; indiquer les évènements motivant dépréciation et reprise.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B22,C9:C22,D9:D22,F14:F22,G14:G22,H14:H22)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B22,C9:C22,D9:D22,F14:F22,G14:G22,H14:H22)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -10710,7 +10719,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -10736,7 +10745,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -10762,7 +10771,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -10788,7 +10797,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -10814,7 +10823,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -10829,18 +10838,18 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"472*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"475*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"471*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"471*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"472*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"475*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"472*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"475*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"471*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"471*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"472*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"475*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -10855,18 +10864,18 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D15" s="120">
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -10892,7 +10901,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -10907,18 +10916,18 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -10940,7 +10949,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -10966,7 +10975,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -10983,21 +10992,21 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="122" t="inlineStr">
+      <c r="A22" s="123" t="inlineStr">
         <is>
           <t>• Justifier toute variation significative ; détailler et justifier les créances significatives ou anciennes.</t>
         </is>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19,F16:F19,G16:G19,H16:H19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19,F16:F19,G16:G19,H16:H19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -11141,7 +11150,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -11164,7 +11173,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -11187,7 +11196,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -11210,7 +11219,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -11233,7 +11242,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -11256,7 +11265,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -11279,7 +11288,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -11302,7 +11311,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -11325,7 +11334,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -11344,7 +11353,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -11367,20 +11376,20 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
     </row>
     <row r="20"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1"/>
-    <row r="23" ht="26" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -11523,7 +11532,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -11546,7 +11555,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -11569,7 +11578,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -11592,7 +11601,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -11615,7 +11624,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="127">
+      <c r="E13" s="128">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -11638,7 +11647,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -11657,7 +11666,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -11680,20 +11689,20 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="127">
+      <c r="E16" s="128">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
     </row>
     <row r="17"/>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="114">
-        <f>IF(SUM(B9:B16,C9:C16,D9:D16)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1"/>
-    <row r="20" ht="26" customHeight="1"/>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="122">
+        <f>IF(SUM(B9:B16,C9:C16,D9:D16)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A18:E20"/>
@@ -11836,7 +11845,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -11859,7 +11868,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -11882,7 +11891,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -11905,7 +11914,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -11928,7 +11937,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -11951,7 +11960,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -11963,18 +11972,18 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"532*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"538*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"533*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"532*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"533*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"538*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"532*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"538*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"533*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"532*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"533*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"538*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D15" s="120">
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -11997,7 +12006,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -12020,7 +12029,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -12043,7 +12052,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -12066,7 +12075,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -12078,18 +12087,18 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -12108,7 +12117,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="127">
+      <c r="E21" s="128">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -12131,7 +12140,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="127">
+      <c r="E22" s="128">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -12145,21 +12154,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la date de rapprochement des comptes bancaires et la date d'inventaire de la caisse et des instruments de monnaie électronique. NB : les intérêts courus figurent ici en négatif si le compte principal attaché est débiteur.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B22,C9:C22,D9:D22)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B22,C9:C22,D9:D22)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -12302,7 +12311,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -12336,7 +12345,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -12361,21 +12370,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>• Détailler par devise : montant en devises, cours UML à l'année d'acquisition, cours UML au 31/12.</t>
         </is>
       </c>
     </row>
     <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="114">
-        <f>IF(SUM(B9:B12,C9:C12,D9:D12)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1"/>
-    <row r="19" ht="26" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="122">
+        <f>IF(SUM(B9:B12,C9:C12,D9:D12)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A17:E19"/>
@@ -12518,7 +12527,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -12541,7 +12550,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -12564,7 +12573,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -12587,7 +12596,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="128">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -12644,14 +12653,14 @@
       <c r="E17" s="119" t="n"/>
     </row>
     <row r="18"/>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="114">
-        <f>IF(SUM(B9:B17,C9:C17,D9:D17)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1"/>
-    <row r="21" ht="26" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="122">
+        <f>IF(SUM(B9:B17,C9:C17,D9:D17)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -12794,7 +12803,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -12817,7 +12826,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -12840,7 +12849,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="127">
+      <c r="E11" s="128">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -12863,7 +12872,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -12877,21 +12886,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la date des délibérations ou dispositions statutaires justifiant la variation des réserves et du report à nouveau.</t>
         </is>
       </c>
     </row>
     <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="114">
-        <f>IF(SUM(B9:B12,C9:C12,D9:D12)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1"/>
-    <row r="19" ht="26" customHeight="1"/>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="122">
+        <f>IF(SUM(B9:B12,C9:C12,D9:D12)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A17:E19"/>
@@ -13046,7 +13055,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -13071,7 +13080,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -13096,7 +13105,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -13121,7 +13130,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -13146,7 +13155,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -13171,7 +13180,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -13196,7 +13205,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -13221,7 +13230,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -13246,7 +13255,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -13271,7 +13280,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -13292,7 +13301,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -13317,7 +13326,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="128">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -13333,21 +13342,21 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="122" t="inlineStr">
+      <c r="A23" s="123" t="inlineStr">
         <is>
           <t>• Indiquer pour chaque subvention la date d'octroi, la nature, les obligations éventuelles ; pour les provisions réglementées, le texte de référence.</t>
         </is>
       </c>
     </row>
     <row r="24"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="114">
-        <f>IF(SUM(B9:B20,C9:C20,D9:D20,F17:F20,G17:G20)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1"/>
-    <row r="27" ht="26" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="122">
+        <f>IF(SUM(B9:B20,C9:C20,D9:D20,F17:F20,G17:G20)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A25:G27"/>
@@ -13480,18 +13489,18 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D9" s="120">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -13514,7 +13523,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -13537,7 +13546,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -13560,7 +13569,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -13583,7 +13592,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="127">
+      <c r="E13" s="128">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -13606,7 +13615,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -13629,7 +13638,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -13652,7 +13661,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -13675,7 +13684,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -13698,7 +13707,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -13712,21 +13721,21 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="122" t="inlineStr">
+      <c r="A21" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la date d'affectation des fonds et leur mode de reprise ; la date des actes de donation et legs, la nature et la durée de jouissance de l'usufruit.</t>
         </is>
       </c>
     </row>
     <row r="22"/>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="114">
-        <f>IF(SUM(B9:B18,C9:C18,D9:D18)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1"/>
-    <row r="25" ht="26" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="122">
+        <f>IF(SUM(B9:B18,C9:C18,D9:D18)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -13887,7 +13896,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -13913,7 +13922,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -13939,7 +13948,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -13965,7 +13974,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -13991,7 +14000,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -14017,7 +14026,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -14043,7 +14052,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -14069,7 +14078,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -14095,7 +14104,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -14121,7 +14130,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -14147,7 +14156,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -14162,18 +14171,18 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -14199,7 +14208,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="127">
+      <c r="E21" s="128">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -14225,7 +14234,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -14251,7 +14260,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -14277,7 +14286,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -14303,7 +14312,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="126">
+      <c r="E25" s="127">
         <f>IF(C25=0,"",(B25-C25)/C25)</f>
         <v/>
       </c>
@@ -14329,7 +14338,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="126">
+      <c r="E26" s="127">
         <f>IF(C26=0,"",(B26-C26)/C26)</f>
         <v/>
       </c>
@@ -14355,7 +14364,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="127">
+      <c r="E27" s="128">
         <f>IF(C27=0,"",(B27-C27)/C27)</f>
         <v/>
       </c>
@@ -14381,7 +14390,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="127">
+      <c r="E28" s="128">
         <f>IF(C28=0,"",(B28-C28)/C28)</f>
         <v/>
       </c>
@@ -14398,21 +14407,21 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="122" t="inlineStr">
+      <c r="A31" s="123" t="inlineStr">
         <is>
           <t>• Pour chaque emprunt et dette de location-acquisition : date d'octroi, organisme, montant initial, durée, garanties données ; pour les pensions, méthode d'évaluation et descriptif de la convention.</t>
         </is>
       </c>
     </row>
     <row r="32"/>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="114">
-        <f>IF(SUM(B9:B28,C9:C28,D9:D28,F15:F28,G15:G28,H15:H28)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1"/>
-    <row r="35" ht="26" customHeight="1"/>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="122">
+        <f>IF(SUM(B9:B28,C9:C28,D9:D28,F15:F28,G15:G28,H15:H28)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1"/>
+    <row r="35" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -14821,7 +14830,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>Actif éventuel (litiges, ...) : année N / année N-1.</t>
         </is>
@@ -14830,7 +14839,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>Passif éventuel (litiges, ...) : année N / année N-1.</t>
         </is>
@@ -14839,7 +14848,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>Décrire les principales caractéristiques, l'horizon des encaissements/décaissements attendus et les éventuels remboursements à percevoir.</t>
         </is>
@@ -15009,18 +15018,18 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D9" s="120">
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -15046,7 +15055,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -15072,7 +15081,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -15098,7 +15107,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -15124,7 +15133,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -15150,7 +15159,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -15186,7 +15195,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -15212,7 +15221,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -15238,7 +15247,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -15264,7 +15273,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -15273,14 +15282,14 @@
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19,F14:F19,G14:G19,H14:H19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1"/>
-    <row r="23" ht="26" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19,F14:F19,G14:G19,H14:H19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -15442,7 +15451,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -15468,7 +15477,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -15494,7 +15503,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -15509,18 +15518,18 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"427*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"425*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"423*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"424*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"428*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"421*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4281*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"427*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"425*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"424*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"428*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"421*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"423*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4281*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"427*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"425*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"423*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"424*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"428*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"421*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4281*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"427*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"425*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"424*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"428*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"421*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"423*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4281*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D12" s="120">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -15546,7 +15555,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -15572,7 +15581,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -15598,7 +15607,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -15624,7 +15633,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -15650,7 +15659,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -15676,7 +15685,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -15702,7 +15711,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -15717,18 +15726,18 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"443*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"444*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"445*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"444*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"445*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"443*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"443*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"444*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"445*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"444*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"445*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"443*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -15754,7 +15763,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -15769,18 +15778,18 @@
         </is>
       </c>
       <c r="B22" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"449*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"448*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"448*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"449*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C22" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"449*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"448*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"448*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"449*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D22" s="120">
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -15806,7 +15815,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="127">
+      <c r="E23" s="128">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -15832,7 +15841,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="127">
+      <c r="E24" s="128">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -15849,21 +15858,21 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="122" t="inlineStr">
+      <c r="A27" s="123" t="inlineStr">
         <is>
           <t>• Commenter toute variation significative et les dettes anciennes.</t>
         </is>
       </c>
     </row>
     <row r="28"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="114">
-        <f>IF(SUM(B9:B24,C9:C24,D9:D24,F18:F24,G18:G24,H18:H24)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1"/>
-    <row r="31" ht="26" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="122">
+        <f>IF(SUM(B9:B24,C9:C24,D9:D24,F18:F24,G18:G24,H18:H24)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1"/>
+    <row r="31" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -16008,18 +16017,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>Fonds d'administration des projets</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="128" t="n"/>
-      <c r="F9" s="128" t="n"/>
-      <c r="G9" s="128" t="n"/>
-      <c r="H9" s="128" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="129" t="n"/>
+      <c r="F9" s="129" t="n"/>
+      <c r="G9" s="129" t="n"/>
+      <c r="H9" s="129" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -16039,7 +16048,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -16065,7 +16074,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -16091,7 +16100,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -16117,7 +16126,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="127">
+      <c r="E13" s="128">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -16132,18 +16141,18 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4719*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4712*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4711*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4717*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4712*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4717*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4719*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4711*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4719*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4712*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4711*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4717*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4712*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4717*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4719*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4711*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -16169,7 +16178,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -16195,7 +16204,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -16221,7 +16230,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -16236,18 +16245,18 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4721*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4721*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4721*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4721*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D18" s="120">
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -16273,7 +16282,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -16299,7 +16308,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="128">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -16335,7 +16344,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -16352,21 +16361,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="122" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>• Commenter toute variation significative et les dettes anciennes.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B22,C9:C22,D9:D22,F13:F20,G13:G20,H13:H20)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B22,C9:C22,D9:D22,F13:F20,G13:G20,H13:H20)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -16510,7 +16519,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -16533,7 +16542,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -16545,18 +16554,18 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"524*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"525*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"523*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"525*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"524*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"523*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"524*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"525*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"523*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"525*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"524*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"523*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D11" s="120">
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -16568,18 +16577,18 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"566*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"526*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"526*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"566*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"566*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"526*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"526*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"566*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D12" s="120">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -16602,7 +16611,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -16625,7 +16634,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -16639,21 +16648,21 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="122" t="inlineStr">
+      <c r="A17" s="123" t="inlineStr">
         <is>
           <t>• Indiquer l'organisme, les conditions de crédit, le taux d'intérêt, la durée. NB : « Banques, intérêts courus » figure ici si le compte principal attaché est créditeur.</t>
         </is>
       </c>
     </row>
     <row r="18"/>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="114">
-        <f>IF(SUM(B9:B14,C9:C14,D9:D14)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1"/>
-    <row r="21" ht="26" customHeight="1"/>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="122">
+        <f>IF(SUM(B9:B14,C9:C14,D9:D14)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -16796,7 +16805,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -16819,7 +16828,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -16842,7 +16851,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -16865,7 +16874,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -16888,7 +16897,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -16900,18 +16909,18 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -16934,7 +16943,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -16957,7 +16966,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -16969,18 +16978,18 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -17003,7 +17012,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -17026,7 +17035,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -17040,21 +17049,21 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="122" t="inlineStr">
+      <c r="A22" s="123" t="inlineStr">
         <is>
           <t>• Justifier toute variation significative ; détailler les revenus liés à la générosité (dons, legs, deniers du culte, zakat, célébrations, mécénat, parrainage).</t>
         </is>
       </c>
     </row>
     <row r="23"/>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1"/>
+    <row r="26" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -17197,7 +17206,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -17220,7 +17229,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="127">
+      <c r="E10" s="128">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -17243,7 +17252,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -17266,7 +17275,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="127">
+      <c r="E12" s="128">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -17289,7 +17298,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -17312,7 +17321,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -17335,7 +17344,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -17358,7 +17367,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -17381,7 +17390,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -17404,7 +17413,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -17427,20 +17436,20 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="128">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
     </row>
     <row r="20"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="114">
-        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1"/>
-    <row r="23" ht="26" customHeight="1"/>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="122">
+        <f>IF(SUM(B9:B19,C9:C19,D9:D19)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1"/>
+    <row r="23" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -17583,7 +17592,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -17606,7 +17615,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -17629,7 +17638,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -17652,7 +17661,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -17675,7 +17684,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -17698,20 +17707,20 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="127">
+      <c r="E14" s="128">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
     </row>
     <row r="15"/>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="114">
-        <f>IF(SUM(B9:B14,C9:C14,D9:D14)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1"/>
-    <row r="18" ht="26" customHeight="1"/>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="122">
+        <f>IF(SUM(B9:B14,C9:C14,D9:D14)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1"/>
+    <row r="18" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -17854,7 +17863,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -17877,7 +17886,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -17900,7 +17909,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -17923,7 +17932,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -17946,7 +17955,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -17969,7 +17978,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -17992,7 +18001,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -18015,7 +18024,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -18038,7 +18047,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -18061,7 +18070,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -18084,7 +18093,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -18107,7 +18116,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -18130,7 +18139,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -18153,7 +18162,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -18176,7 +18185,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -18199,7 +18208,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -18222,20 +18231,20 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="127">
+      <c r="E25" s="128">
         <f>IF(C25=0,"",(B25-C25)/C25)</f>
         <v/>
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B9:B25,C9:C25,D9:D25)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B9:B25,C9:C25,D9:D25)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -18378,7 +18387,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -18401,7 +18410,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -18424,7 +18433,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -18447,7 +18456,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -18470,7 +18479,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -18493,7 +18502,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -18516,7 +18525,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -18530,21 +18539,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>• Détailler pénalités et amendes et en indiquer la cause.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="114">
-        <f>IF(SUM(B9:B15,C9:C15,D9:D15)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="122">
+        <f>IF(SUM(B9:B15,C9:C15,D9:D15)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1"/>
+    <row r="22" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A20:E22"/>
@@ -19084,7 +19093,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -19107,7 +19116,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -19130,7 +19139,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -19153,7 +19162,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -19176,7 +19185,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -19199,7 +19208,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -19222,7 +19231,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="127">
+      <c r="E15" s="128">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -19236,21 +19245,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>• Indiquer les bénéficiaires des subventions versées.</t>
         </is>
       </c>
     </row>
     <row r="19"/>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="114">
-        <f>IF(SUM(B9:B15,C9:C15,D9:D15)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1"/>
-    <row r="22" ht="26" customHeight="1"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="122">
+        <f>IF(SUM(B9:B15,C9:C15,D9:D15)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1"/>
+    <row r="22" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A20:E22"/>
@@ -19393,7 +19402,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -19416,7 +19425,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -19439,7 +19448,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -19462,7 +19471,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -19485,7 +19494,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -19508,7 +19517,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -19531,7 +19540,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -19554,7 +19563,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -19577,7 +19586,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -19591,21 +19600,21 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="122" t="inlineStr">
+      <c r="A20" s="123" t="inlineStr">
         <is>
           <t>• Indiquer la nature et la durée du contrat du personnel extérieur.</t>
         </is>
       </c>
     </row>
     <row r="21"/>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="114">
-        <f>IF(SUM(B9:B17,C9:C17,D9:D17)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1"/>
-    <row r="24" ht="26" customHeight="1"/>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="122">
+        <f>IF(SUM(B9:B17,C9:C17,D9:D17)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1"/>
+    <row r="24" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A22:E24"/>
@@ -19931,14 +19940,14 @@
       </c>
     </row>
     <row r="26"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="114">
-        <f>IF(SUM(B24:B24,F10:F14,G10:G14,H10:H14,I10:I14)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="122">
+        <f>IF(SUM(B24:B24,F10:F14,G10:G14,H10:H14,I10:I14)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B4:F4"/>
@@ -20324,17 +20333,17 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
       <c r="E17" s="120" t="n"/>
       <c r="F17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="G17" s="120" t="n"/>
@@ -20674,14 +20683,14 @@
       </c>
     </row>
     <row r="31"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="114">
-        <f>IF(SUM(B9:B28,C9:C28,D9:D28,E9:E28,F9:F28,G9:G28,H9:H28,I9:I28)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1"/>
-    <row r="34" ht="26" customHeight="1"/>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="122">
+        <f>IF(SUM(B9:B28,C9:C28,D9:D28,E9:E28,F9:F28,G9:G28,H9:H28,I9:I28)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1"/>
+    <row r="34" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B4:F4"/>
@@ -20825,7 +20834,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -20848,7 +20857,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -20871,7 +20880,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -20894,7 +20903,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -20917,7 +20926,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -20940,7 +20949,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -20963,7 +20972,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -20986,7 +20995,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -21009,7 +21018,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="128">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -21032,7 +21041,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -21055,7 +21064,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -21078,7 +21087,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -21101,7 +21110,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -21124,7 +21133,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -21147,7 +21156,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -21170,7 +21179,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -21193,7 +21202,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="126">
+      <c r="E25" s="127">
         <f>IF(C25=0,"",(B25-C25)/C25)</f>
         <v/>
       </c>
@@ -21216,7 +21225,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="126">
+      <c r="E26" s="127">
         <f>IF(C26=0,"",(B26-C26)/C26)</f>
         <v/>
       </c>
@@ -21239,7 +21248,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="127">
+      <c r="E27" s="128">
         <f>IF(C27=0,"",(B27-C27)/C27)</f>
         <v/>
       </c>
@@ -21262,20 +21271,20 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="127">
+      <c r="E28" s="128">
         <f>IF(C28=0,"",(B28-C28)/C28)</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="114">
-        <f>IF(SUM(B9:B28,C9:C28,D9:D28)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1"/>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="122">
+        <f>IF(SUM(B9:B28,C9:C28,D9:D28)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1"/>
+    <row r="32" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -21418,7 +21427,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="126">
+      <c r="E9" s="127">
         <f>IF(C9=0,"",(B9-C9)/C9)</f>
         <v/>
       </c>
@@ -21441,7 +21450,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(C10=0,"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -21464,7 +21473,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(C11=0,"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -21487,7 +21496,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(C12=0,"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -21510,7 +21519,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(C13=0,"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -21533,7 +21542,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(C14=0,"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -21556,7 +21565,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="126">
+      <c r="E15" s="127">
         <f>IF(C15=0,"",(B15-C15)/C15)</f>
         <v/>
       </c>
@@ -21579,7 +21588,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="126">
+      <c r="E16" s="127">
         <f>IF(C16=0,"",(B16-C16)/C16)</f>
         <v/>
       </c>
@@ -21602,7 +21611,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(C17=0,"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -21625,7 +21634,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="127">
+      <c r="E18" s="128">
         <f>IF(C18=0,"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -21648,7 +21657,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="126">
+      <c r="E19" s="127">
         <f>IF(C19=0,"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -21671,7 +21680,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(C20=0,"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -21694,7 +21703,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(C21=0,"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -21717,7 +21726,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="E22" s="126">
+      <c r="E22" s="127">
         <f>IF(C22=0,"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -21740,7 +21749,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(C23=0,"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -21763,7 +21772,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(C24=0,"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -21786,7 +21795,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="E25" s="126">
+      <c r="E25" s="127">
         <f>IF(C25=0,"",(B25-C25)/C25)</f>
         <v/>
       </c>
@@ -21809,7 +21818,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="E26" s="126">
+      <c r="E26" s="127">
         <f>IF(C26=0,"",(B26-C26)/C26)</f>
         <v/>
       </c>
@@ -21832,7 +21841,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="126">
+      <c r="E27" s="127">
         <f>IF(C27=0,"",(B27-C27)/C27)</f>
         <v/>
       </c>
@@ -21855,7 +21864,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="127">
+      <c r="E28" s="128">
         <f>IF(C28=0,"",(B28-C28)/C28)</f>
         <v/>
       </c>
@@ -21878,20 +21887,20 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="127">
+      <c r="E29" s="128">
         <f>IF(C29=0,"",(B29-C29)/C29)</f>
         <v/>
       </c>
     </row>
     <row r="30"/>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="114">
-        <f>IF(SUM(B9:B29,C9:C29,D9:D29)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1"/>
-    <row r="33" ht="26" customHeight="1"/>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="122">
+        <f>IF(SUM(B9:B29,C9:C29,D9:D29)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1"/>
+    <row r="33" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A7:E7"/>
@@ -21987,42 +21996,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="129" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>(en unités monétaires légales)</t>
         </is>
       </c>
-      <c r="B8" s="130" t="inlineStr">
+      <c r="B8" s="131" t="inlineStr">
         <is>
           <t>Année N</t>
         </is>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>Année N-1</t>
         </is>
       </c>
-      <c r="D8" s="130" t="inlineStr">
+      <c r="D8" s="131" t="inlineStr">
         <is>
           <t>Variation en valeur</t>
         </is>
       </c>
-      <c r="E8" s="129" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Variation en %</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="inlineStr">
+      <c r="A9" s="124" t="inlineStr">
         <is>
           <t>ANALYSE DE L'ACTIVITÉ - SOLDES INTERMÉDIAIRES DE GESTION</t>
         </is>
       </c>
-      <c r="B9" s="124" t="n"/>
-      <c r="C9" s="124" t="n"/>
-      <c r="D9" s="124" t="n"/>
-      <c r="E9" s="128" t="n"/>
+      <c r="B9" s="125" t="n"/>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="125" t="n"/>
+      <c r="E9" s="129" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="119" t="inlineStr">
@@ -22042,7 +22051,7 @@
         <f>IF(OR(B10="",C10=""),"",B10-C10)</f>
         <v/>
       </c>
-      <c r="E10" s="126">
+      <c r="E10" s="127">
         <f>IF(OR(C10="",C10=0),"",(B10-C10)/C10)</f>
         <v/>
       </c>
@@ -22065,7 +22074,7 @@
         <f>IF(OR(B11="",C11=""),"",B11-C11)</f>
         <v/>
       </c>
-      <c r="E11" s="126">
+      <c r="E11" s="127">
         <f>IF(OR(C11="",C11=0),"",(B11-C11)/C11)</f>
         <v/>
       </c>
@@ -22088,7 +22097,7 @@
         <f>IF(OR(B12="",C12=""),"",B12-C12)</f>
         <v/>
       </c>
-      <c r="E12" s="126">
+      <c r="E12" s="127">
         <f>IF(OR(C12="",C12=0),"",(B12-C12)/C12)</f>
         <v/>
       </c>
@@ -22100,18 +22109,18 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D13" s="120">
         <f>IF(OR(B13="",C13=""),"",B13-C13)</f>
         <v/>
       </c>
-      <c r="E13" s="126">
+      <c r="E13" s="127">
         <f>IF(OR(C13="",C13=0),"",(B13-C13)/C13)</f>
         <v/>
       </c>
@@ -22134,7 +22143,7 @@
         <f>IF(OR(B14="",C14=""),"",B14-C14)</f>
         <v/>
       </c>
-      <c r="E14" s="126">
+      <c r="E14" s="127">
         <f>IF(OR(C14="",C14=0),"",(B14-C14)/C14)</f>
         <v/>
       </c>
@@ -22151,15 +22160,15 @@
       <c r="E15" s="119" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="123" t="inlineStr">
+      <c r="A16" s="124" t="inlineStr">
         <is>
           <t>ANALYSE DE LA STRUCTURE FINANCIÈRE</t>
         </is>
       </c>
-      <c r="B16" s="124" t="n"/>
-      <c r="C16" s="124" t="n"/>
-      <c r="D16" s="124" t="n"/>
-      <c r="E16" s="128" t="n"/>
+      <c r="B16" s="125" t="n"/>
+      <c r="C16" s="125" t="n"/>
+      <c r="D16" s="125" t="n"/>
+      <c r="E16" s="129" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="119" t="inlineStr">
@@ -22179,7 +22188,7 @@
         <f>IF(OR(B17="",C17=""),"",B17-C17)</f>
         <v/>
       </c>
-      <c r="E17" s="126">
+      <c r="E17" s="127">
         <f>IF(OR(C17="",C17=0),"",(B17-C17)/C17)</f>
         <v/>
       </c>
@@ -22202,7 +22211,7 @@
         <f>IF(OR(B18="",C18=""),"",B18-C18)</f>
         <v/>
       </c>
-      <c r="E18" s="126">
+      <c r="E18" s="127">
         <f>IF(OR(C18="",C18=0),"",(B18-C18)/C18)</f>
         <v/>
       </c>
@@ -22225,7 +22234,7 @@
         <f>IF(OR(B19="",C19=""),"",B19-C19)</f>
         <v/>
       </c>
-      <c r="E19" s="131">
+      <c r="E19" s="132">
         <f>IF(OR(C19="",C19=0),"",(B19-C19)/C19)</f>
         <v/>
       </c>
@@ -22248,7 +22257,7 @@
         <f>IF(OR(B20="",C20=""),"",B20-C20)</f>
         <v/>
       </c>
-      <c r="E20" s="126">
+      <c r="E20" s="127">
         <f>IF(OR(C20="",C20=0),"",(B20-C20)/C20)</f>
         <v/>
       </c>
@@ -22271,7 +22280,7 @@
         <f>IF(OR(B21="",C21=""),"",B21-C21)</f>
         <v/>
       </c>
-      <c r="E21" s="126">
+      <c r="E21" s="127">
         <f>IF(OR(C21="",C21=0),"",(B21-C21)/C21)</f>
         <v/>
       </c>
@@ -22294,7 +22303,7 @@
         <f>IF(OR(B22="",C22=""),"",B22-C22)</f>
         <v/>
       </c>
-      <c r="E22" s="131">
+      <c r="E22" s="132">
         <f>IF(OR(C22="",C22=0),"",(B22-C22)/C22)</f>
         <v/>
       </c>
@@ -22317,7 +22326,7 @@
         <f>IF(OR(B23="",C23=""),"",B23-C23)</f>
         <v/>
       </c>
-      <c r="E23" s="126">
+      <c r="E23" s="127">
         <f>IF(OR(C23="",C23=0),"",(B23-C23)/C23)</f>
         <v/>
       </c>
@@ -22340,7 +22349,7 @@
         <f>IF(OR(B24="",C24=""),"",B24-C24)</f>
         <v/>
       </c>
-      <c r="E24" s="126">
+      <c r="E24" s="127">
         <f>IF(OR(C24="",C24=0),"",(B24-C24)/C24)</f>
         <v/>
       </c>
@@ -22363,7 +22372,7 @@
         <f>IF(OR(B25="",C25=""),"",B25-C25)</f>
         <v/>
       </c>
-      <c r="E25" s="131">
+      <c r="E25" s="132">
         <f>IF(OR(C25="",C25=0),"",(B25-C25)/C25)</f>
         <v/>
       </c>
@@ -22386,7 +22395,7 @@
         <f>IF(OR(B26="",C26=""),"",B26-C26)</f>
         <v/>
       </c>
-      <c r="E26" s="131">
+      <c r="E26" s="132">
         <f>IF(OR(C26="",C26=0),"",(B26-C26)/C26)</f>
         <v/>
       </c>
@@ -22409,7 +22418,7 @@
         <f>IF(OR(B27="",C27=""),"",B27-C27)</f>
         <v/>
       </c>
-      <c r="E27" s="131">
+      <c r="E27" s="132">
         <f>IF(OR(C27="",C27=0),"",(B27-C27)/C27)</f>
         <v/>
       </c>
@@ -22432,21 +22441,21 @@
         <f>IF(OR(B28="",C28=""),"",B28-C28)</f>
         <v/>
       </c>
-      <c r="E28" s="126">
+      <c r="E28" s="127">
         <f>IF(OR(C28="",C28=0),"",(B28-C28)/C28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="123" t="inlineStr">
+      <c r="A29" s="124" t="inlineStr">
         <is>
           <t>ANALYSE DE LA SOLVABILITÉ</t>
         </is>
       </c>
-      <c r="B29" s="124" t="n"/>
-      <c r="C29" s="124" t="n"/>
-      <c r="D29" s="124" t="n"/>
-      <c r="E29" s="128" t="n"/>
+      <c r="B29" s="125" t="n"/>
+      <c r="C29" s="125" t="n"/>
+      <c r="D29" s="125" t="n"/>
+      <c r="E29" s="129" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="119" t="inlineStr">
@@ -22466,21 +22475,21 @@
         <f>IF(OR(B30="",C30=""),"",B30-C30)</f>
         <v/>
       </c>
-      <c r="E30" s="126">
+      <c r="E30" s="127">
         <f>IF(OR(C30="",C30=0),"",(B30-C30)/C30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="123" t="inlineStr">
+      <c r="A31" s="124" t="inlineStr">
         <is>
           <t>ANALYSE DE LA VARIATION DE LA TRÉSORERIE</t>
         </is>
       </c>
-      <c r="B31" s="124" t="n"/>
-      <c r="C31" s="124" t="n"/>
-      <c r="D31" s="124" t="n"/>
-      <c r="E31" s="128" t="n"/>
+      <c r="B31" s="125" t="n"/>
+      <c r="C31" s="125" t="n"/>
+      <c r="D31" s="125" t="n"/>
+      <c r="E31" s="129" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="119" t="inlineStr">
@@ -22500,7 +22509,7 @@
         <f>IF(OR(B32="",C32=""),"",B32-C32)</f>
         <v/>
       </c>
-      <c r="E32" s="126">
+      <c r="E32" s="127">
         <f>IF(OR(C32="",C32=0),"",(B32-C32)/C32)</f>
         <v/>
       </c>
@@ -22523,7 +22532,7 @@
         <f>IF(OR(B33="",C33=""),"",B33-C33)</f>
         <v/>
       </c>
-      <c r="E33" s="126">
+      <c r="E33" s="127">
         <f>IF(OR(C33="",C33=0),"",(B33-C33)/C33)</f>
         <v/>
       </c>
@@ -22546,7 +22555,7 @@
         <f>IF(OR(B34="",C34=""),"",B34-C34)</f>
         <v/>
       </c>
-      <c r="E34" s="126">
+      <c r="E34" s="127">
         <f>IF(OR(C34="",C34=0),"",(B34-C34)/C34)</f>
         <v/>
       </c>
@@ -22569,7 +22578,7 @@
         <f>IF(OR(B35="",C35=""),"",B35-C35)</f>
         <v/>
       </c>
-      <c r="E35" s="126">
+      <c r="E35" s="127">
         <f>IF(OR(C35="",C35=0),"",(B35-C35)/C35)</f>
         <v/>
       </c>
@@ -22583,14 +22592,14 @@
       </c>
     </row>
     <row r="38"/>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="114">
-        <f>IF(SUM(B8:B35,C8:C35,D8:D35)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="26" customHeight="1"/>
-    <row r="41" ht="26" customHeight="1"/>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="122">
+        <f>IF(SUM(B8:B35,C8:C35,D8:D35)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1"/>
+    <row r="41" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A39:E41"/>
@@ -22689,7 +22698,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="122" t="inlineStr">
+      <c r="A9" s="123" t="inlineStr">
         <is>
           <t>(Note obligatoire pour les entités de plus de 250 personnes, bénévoles compris.)</t>
         </is>
@@ -22698,7 +22707,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>INFORMATIONS SOCIALES : emploi (effectif total, répartition par sexe, âge et zone géographique ; embauches et licenciements ; rémunérations et leur évolution) ; relations sociales ; santé et sécurité ; formation ; égalité de traitement.</t>
         </is>
@@ -22707,7 +22716,7 @@
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="123" t="inlineStr">
         <is>
           <t>INFORMATIONS ENVIRONNEMENTALES : politique générale ; pollution et gestion des déchets ; utilisation durable des ressources ; changement climatique ; protection de la biodiversité.</t>
         </is>
@@ -22716,7 +22725,7 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18">
-      <c r="A18" s="122" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>ENGAGEMENTS SOCIÉTAUX EN FAVEUR DU DÉVELOPPEMENT DURABLE : impact territorial, économique et social ; relations avec les parties prenantes ; sous-traitance et fournisseurs.</t>
         </is>
@@ -22894,7 +22903,7 @@
         <f>C9-F9</f>
         <v/>
       </c>
-      <c r="H9" s="126">
+      <c r="H9" s="127">
         <f>IF(C9=0,"",F9/C9)</f>
         <v/>
       </c>
@@ -22913,7 +22922,7 @@
         <f>C10-F10</f>
         <v/>
       </c>
-      <c r="H10" s="126">
+      <c r="H10" s="127">
         <f>IF(C10=0,"",F10/C10)</f>
         <v/>
       </c>
@@ -22932,7 +22941,7 @@
         <f>C11-F11</f>
         <v/>
       </c>
-      <c r="H11" s="126">
+      <c r="H11" s="127">
         <f>IF(C11=0,"",F11/C11)</f>
         <v/>
       </c>
@@ -22951,7 +22960,7 @@
         <f>C12-F12</f>
         <v/>
       </c>
-      <c r="H12" s="126">
+      <c r="H12" s="127">
         <f>IF(C12=0,"",F12/C12)</f>
         <v/>
       </c>
@@ -22970,7 +22979,7 @@
         <f>C13-F13</f>
         <v/>
       </c>
-      <c r="H13" s="126">
+      <c r="H13" s="127">
         <f>IF(C13=0,"",F13/C13)</f>
         <v/>
       </c>
@@ -22989,7 +22998,7 @@
         <f>C14-F14</f>
         <v/>
       </c>
-      <c r="H14" s="126">
+      <c r="H14" s="127">
         <f>IF(C14=0,"",F14/C14)</f>
         <v/>
       </c>
@@ -23008,7 +23017,7 @@
         <f>C15-F15</f>
         <v/>
       </c>
-      <c r="H15" s="126">
+      <c r="H15" s="127">
         <f>IF(C15=0,"",F15/C15)</f>
         <v/>
       </c>
@@ -23027,7 +23036,7 @@
         <f>C16-F16</f>
         <v/>
       </c>
-      <c r="H16" s="126">
+      <c r="H16" s="127">
         <f>IF(C16=0,"",F16/C16)</f>
         <v/>
       </c>
@@ -23046,7 +23055,7 @@
         <f>C17-F17</f>
         <v/>
       </c>
-      <c r="H17" s="126">
+      <c r="H17" s="127">
         <f>IF(C17=0,"",F17/C17)</f>
         <v/>
       </c>
@@ -23065,7 +23074,7 @@
         <f>C18-F18</f>
         <v/>
       </c>
-      <c r="H18" s="126">
+      <c r="H18" s="127">
         <f>IF(C18=0,"",F18/C18)</f>
         <v/>
       </c>
@@ -23084,7 +23093,7 @@
         <f>C19-F19</f>
         <v/>
       </c>
-      <c r="H19" s="126">
+      <c r="H19" s="127">
         <f>IF(C19=0,"",F19/C19)</f>
         <v/>
       </c>
@@ -23103,7 +23112,7 @@
         <f>C20-F20</f>
         <v/>
       </c>
-      <c r="H20" s="126">
+      <c r="H20" s="127">
         <f>IF(C20=0,"",F20/C20)</f>
         <v/>
       </c>
@@ -23135,7 +23144,7 @@
         <f>SUM(G9:G20)</f>
         <v/>
       </c>
-      <c r="H21" s="131">
+      <c r="H21" s="132">
         <f>IF(C21=0,"",F21/C21)</f>
         <v/>
       </c>
@@ -23149,14 +23158,14 @@
       </c>
     </row>
     <row r="24"/>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="114">
-        <f>IF(SUM(C9:C21,D9:D21,E9:E21,F9:F21,G9:G21)=0,"NÉANT - NOTE NON RENSEIGNÉE","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1"/>
-    <row r="27" ht="26" customHeight="1"/>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="122">
+        <f>IF(SUM(C9:C21,D9:D21,E9:E21,F9:F21,G9:G21)=0,"NÉANT","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1"/>
+    <row r="27" ht="34" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A7:H7"/>
@@ -23193,7 +23202,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G1" s="132" t="inlineStr">
+      <c r="G1" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 1/12</t>
@@ -23245,26 +23254,26 @@
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="133" t="inlineStr">
+      <c r="A6" s="134" t="inlineStr">
         <is>
           <t>Partie 1 : Informations générales</t>
         </is>
       </c>
-      <c r="B6" s="134" t="n"/>
-      <c r="C6" s="134" t="n"/>
-      <c r="D6" s="134" t="n"/>
-      <c r="E6" s="134" t="n"/>
-      <c r="F6" s="134" t="n"/>
-      <c r="G6" s="134" t="n"/>
-      <c r="H6" s="134" t="n"/>
+      <c r="B6" s="135" t="n"/>
+      <c r="C6" s="135" t="n"/>
+      <c r="D6" s="135" t="n"/>
+      <c r="E6" s="135" t="n"/>
+      <c r="F6" s="135" t="n"/>
+      <c r="G6" s="135" t="n"/>
+      <c r="H6" s="135" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="135" t="inlineStr">
+      <c r="A7" s="136" t="inlineStr">
         <is>
           <t>Note 1</t>
         </is>
       </c>
-      <c r="B7" s="136" t="inlineStr">
+      <c r="B7" s="137" t="inlineStr">
         <is>
           <t>DETTES GARANTIES PAR DES SÛRETÉS RÉELLES, ENGAGEMENTS FINANCIERS ET CONTRIBUTIONS VOLONTAIRES EN NATURE</t>
         </is>
@@ -23277,7 +23286,7 @@
       <c r="H7" s="47" t="n"/>
     </row>
     <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="137" t="n"/>
+      <c r="A8" s="138" t="n"/>
       <c r="B8" s="47" t="n"/>
       <c r="C8" s="47" t="n"/>
       <c r="D8" s="47" t="n"/>
@@ -23287,12 +23296,12 @@
       <c r="H8" s="47" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="135" t="inlineStr">
+      <c r="A9" s="136" t="inlineStr">
         <is>
           <t>Note 2</t>
         </is>
       </c>
-      <c r="B9" s="136" t="inlineStr">
+      <c r="B9" s="137" t="inlineStr">
         <is>
           <t>INFORMATIONS OBLIGATOIRES</t>
         </is>
@@ -23305,7 +23314,7 @@
       <c r="H9" s="47" t="n"/>
     </row>
     <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="137" t="n"/>
+      <c r="A10" s="138" t="n"/>
       <c r="B10" s="47" t="n"/>
       <c r="C10" s="47" t="n"/>
       <c r="D10" s="47" t="n"/>
@@ -23315,12 +23324,12 @@
       <c r="H10" s="47" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="135" t="inlineStr">
+      <c r="A11" s="136" t="inlineStr">
         <is>
           <t>Note 3</t>
         </is>
       </c>
-      <c r="B11" s="136" t="inlineStr">
+      <c r="B11" s="137" t="inlineStr">
         <is>
           <t>ÉVÈNEMENTS POSTÉRIEURS À LA CLÔTURE DE L'EXERCICE</t>
         </is>
@@ -23333,7 +23342,7 @@
       <c r="H11" s="47" t="n"/>
     </row>
     <row r="12" ht="110" customHeight="1">
-      <c r="A12" s="137" t="n"/>
+      <c r="A12" s="138" t="n"/>
       <c r="B12" s="47" t="n"/>
       <c r="C12" s="47" t="n"/>
       <c r="D12" s="47" t="n"/>
@@ -23343,12 +23352,12 @@
       <c r="H12" s="47" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="135" t="inlineStr">
+      <c r="A13" s="136" t="inlineStr">
         <is>
           <t>Note 4</t>
         </is>
       </c>
-      <c r="B13" s="136" t="inlineStr">
+      <c r="B13" s="137" t="inlineStr">
         <is>
           <t>CHANGEMENTS DE MÉTHODES COMPTABLES, D'ESTIMATIONS ET CORRECTIONS D'ERREURS</t>
         </is>
@@ -23361,7 +23370,7 @@
       <c r="H13" s="47" t="n"/>
     </row>
     <row r="14" ht="110" customHeight="1">
-      <c r="A14" s="137" t="n"/>
+      <c r="A14" s="138" t="n"/>
       <c r="B14" s="47" t="n"/>
       <c r="C14" s="47" t="n"/>
       <c r="D14" s="47" t="n"/>
@@ -23376,7 +23385,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G15" s="132" t="inlineStr">
+      <c r="G15" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 2/12</t>
@@ -23428,26 +23437,26 @@
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="133" t="inlineStr">
+      <c r="A20" s="134" t="inlineStr">
         <is>
           <t>Partie 2 : Notes sur le bilan</t>
         </is>
       </c>
-      <c r="B20" s="134" t="n"/>
-      <c r="C20" s="134" t="n"/>
-      <c r="D20" s="134" t="n"/>
-      <c r="E20" s="134" t="n"/>
-      <c r="F20" s="134" t="n"/>
-      <c r="G20" s="134" t="n"/>
-      <c r="H20" s="134" t="n"/>
+      <c r="B20" s="135" t="n"/>
+      <c r="C20" s="135" t="n"/>
+      <c r="D20" s="135" t="n"/>
+      <c r="E20" s="135" t="n"/>
+      <c r="F20" s="135" t="n"/>
+      <c r="G20" s="135" t="n"/>
+      <c r="H20" s="135" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="135" t="inlineStr">
+      <c r="A21" s="136" t="inlineStr">
         <is>
           <t>Note 5A</t>
         </is>
       </c>
-      <c r="B21" s="136" t="inlineStr">
+      <c r="B21" s="137" t="inlineStr">
         <is>
           <t>DONS ET LEGS D'IMMOBILISATIONS NON REÇUS DESTINÉS À LA VENTE ET USUFRUIT TEMPORAIRE</t>
         </is>
@@ -23460,7 +23469,7 @@
       <c r="H21" s="47" t="n"/>
     </row>
     <row r="22" ht="110" customHeight="1">
-      <c r="A22" s="137" t="n"/>
+      <c r="A22" s="138" t="n"/>
       <c r="B22" s="47" t="n"/>
       <c r="C22" s="47" t="n"/>
       <c r="D22" s="47" t="n"/>
@@ -23470,12 +23479,12 @@
       <c r="H22" s="47" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="135" t="inlineStr">
+      <c r="A23" s="136" t="inlineStr">
         <is>
           <t>Note 5B</t>
         </is>
       </c>
-      <c r="B23" s="136" t="inlineStr">
+      <c r="B23" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS BRUTES</t>
         </is>
@@ -23488,7 +23497,7 @@
       <c r="H23" s="47" t="n"/>
     </row>
     <row r="24" ht="110" customHeight="1">
-      <c r="A24" s="137" t="n"/>
+      <c r="A24" s="138" t="n"/>
       <c r="B24" s="47" t="n"/>
       <c r="C24" s="47" t="n"/>
       <c r="D24" s="47" t="n"/>
@@ -23498,12 +23507,12 @@
       <c r="H24" s="47" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="135" t="inlineStr">
+      <c r="A25" s="136" t="inlineStr">
         <is>
           <t>Note 5C</t>
         </is>
       </c>
-      <c r="B25" s="136" t="inlineStr">
+      <c r="B25" s="137" t="inlineStr">
         <is>
           <t>BIENS PRIS EN LOCATION-ACQUISITION</t>
         </is>
@@ -23516,7 +23525,7 @@
       <c r="H25" s="47" t="n"/>
     </row>
     <row r="26" ht="110" customHeight="1">
-      <c r="A26" s="137" t="n"/>
+      <c r="A26" s="138" t="n"/>
       <c r="B26" s="47" t="n"/>
       <c r="C26" s="47" t="n"/>
       <c r="D26" s="47" t="n"/>
@@ -23526,12 +23535,12 @@
       <c r="H26" s="47" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="135" t="inlineStr">
+      <c r="A27" s="136" t="inlineStr">
         <is>
           <t>Note 5D</t>
         </is>
       </c>
-      <c r="B27" s="136" t="inlineStr">
+      <c r="B27" s="137" t="inlineStr">
         <is>
           <t>DONS ET LEGS D'IMMOBILISATIONS NON REÇUS DESTINÉS À LA VENTE ET USUFRUIT TEMPORAIRE (AMORTISSEMENTS ET DÉPRÉCIATIONS)</t>
         </is>
@@ -23544,7 +23553,7 @@
       <c r="H27" s="47" t="n"/>
     </row>
     <row r="28" ht="110" customHeight="1">
-      <c r="A28" s="137" t="n"/>
+      <c r="A28" s="138" t="n"/>
       <c r="B28" s="47" t="n"/>
       <c r="C28" s="47" t="n"/>
       <c r="D28" s="47" t="n"/>
@@ -23559,7 +23568,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G29" s="132" t="inlineStr">
+      <c r="G29" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 3/12</t>
@@ -23611,12 +23620,12 @@
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="135" t="inlineStr">
+      <c r="A34" s="136" t="inlineStr">
         <is>
           <t>Note 5E</t>
         </is>
       </c>
-      <c r="B34" s="136" t="inlineStr">
+      <c r="B34" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS : AMORTISSEMENTS</t>
         </is>
@@ -23629,7 +23638,7 @@
       <c r="H34" s="47" t="n"/>
     </row>
     <row r="35" ht="110" customHeight="1">
-      <c r="A35" s="137" t="n"/>
+      <c r="A35" s="138" t="n"/>
       <c r="B35" s="47" t="n"/>
       <c r="C35" s="47" t="n"/>
       <c r="D35" s="47" t="n"/>
@@ -23639,12 +23648,12 @@
       <c r="H35" s="47" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="135" t="inlineStr">
+      <c r="A36" s="136" t="inlineStr">
         <is>
           <t>Note 5F</t>
         </is>
       </c>
-      <c r="B36" s="136" t="inlineStr">
+      <c r="B36" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS : DÉPRÉCIATIONS</t>
         </is>
@@ -23657,7 +23666,7 @@
       <c r="H36" s="47" t="n"/>
     </row>
     <row r="37" ht="110" customHeight="1">
-      <c r="A37" s="137" t="n"/>
+      <c r="A37" s="138" t="n"/>
       <c r="B37" s="47" t="n"/>
       <c r="C37" s="47" t="n"/>
       <c r="D37" s="47" t="n"/>
@@ -23667,12 +23676,12 @@
       <c r="H37" s="47" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="135" t="inlineStr">
+      <c r="A38" s="136" t="inlineStr">
         <is>
           <t>Note 5G</t>
         </is>
       </c>
-      <c r="B38" s="136" t="inlineStr">
+      <c r="B38" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS : PLUS-VALUES ET MOINS-VALUES DE CESSION</t>
         </is>
@@ -23685,7 +23694,7 @@
       <c r="H38" s="47" t="n"/>
     </row>
     <row r="39" ht="110" customHeight="1">
-      <c r="A39" s="137" t="n"/>
+      <c r="A39" s="138" t="n"/>
       <c r="B39" s="47" t="n"/>
       <c r="C39" s="47" t="n"/>
       <c r="D39" s="47" t="n"/>
@@ -23695,12 +23704,12 @@
       <c r="H39" s="47" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="135" t="inlineStr">
+      <c r="A40" s="136" t="inlineStr">
         <is>
           <t>Note 5H</t>
         </is>
       </c>
-      <c r="B40" s="136" t="inlineStr">
+      <c r="B40" s="137" t="inlineStr">
         <is>
           <t>INFORMATIONS SUR LES RÉÉVALUATIONS EFFECTUÉES PAR L'ENTITÉ</t>
         </is>
@@ -23713,7 +23722,7 @@
       <c r="H40" s="47" t="n"/>
     </row>
     <row r="41" ht="110" customHeight="1">
-      <c r="A41" s="137" t="n"/>
+      <c r="A41" s="138" t="n"/>
       <c r="B41" s="47" t="n"/>
       <c r="C41" s="47" t="n"/>
       <c r="D41" s="47" t="n"/>
@@ -23728,7 +23737,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G42" s="132" t="inlineStr">
+      <c r="G42" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 4/12</t>
@@ -23780,12 +23789,12 @@
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="135" t="inlineStr">
+      <c r="A47" s="136" t="inlineStr">
         <is>
           <t>Note 6</t>
         </is>
       </c>
-      <c r="B47" s="136" t="inlineStr">
+      <c r="B47" s="137" t="inlineStr">
         <is>
           <t>IMMOBILISATIONS FINANCIÈRES</t>
         </is>
@@ -23798,7 +23807,7 @@
       <c r="H47" s="47" t="n"/>
     </row>
     <row r="48" ht="110" customHeight="1">
-      <c r="A48" s="137" t="n"/>
+      <c r="A48" s="138" t="n"/>
       <c r="B48" s="47" t="n"/>
       <c r="C48" s="47" t="n"/>
       <c r="D48" s="47" t="n"/>
@@ -23808,12 +23817,12 @@
       <c r="H48" s="47" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="135" t="inlineStr">
+      <c r="A49" s="136" t="inlineStr">
         <is>
           <t>Note 7</t>
         </is>
       </c>
-      <c r="B49" s="136" t="inlineStr">
+      <c r="B49" s="137" t="inlineStr">
         <is>
           <t>ACTIF CIRCULANT ET DETTES CIRCULANTES HAO</t>
         </is>
@@ -23826,7 +23835,7 @@
       <c r="H49" s="47" t="n"/>
     </row>
     <row r="50" ht="110" customHeight="1">
-      <c r="A50" s="137" t="n"/>
+      <c r="A50" s="138" t="n"/>
       <c r="B50" s="47" t="n"/>
       <c r="C50" s="47" t="n"/>
       <c r="D50" s="47" t="n"/>
@@ -23836,12 +23845,12 @@
       <c r="H50" s="47" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="135" t="inlineStr">
+      <c r="A51" s="136" t="inlineStr">
         <is>
           <t>Note 8</t>
         </is>
       </c>
-      <c r="B51" s="136" t="inlineStr">
+      <c r="B51" s="137" t="inlineStr">
         <is>
           <t>STOCKS ET ENCOURS</t>
         </is>
@@ -23854,7 +23863,7 @@
       <c r="H51" s="47" t="n"/>
     </row>
     <row r="52" ht="110" customHeight="1">
-      <c r="A52" s="137" t="n"/>
+      <c r="A52" s="138" t="n"/>
       <c r="B52" s="47" t="n"/>
       <c r="C52" s="47" t="n"/>
       <c r="D52" s="47" t="n"/>
@@ -23864,12 +23873,12 @@
       <c r="H52" s="47" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="135" t="inlineStr">
+      <c r="A53" s="136" t="inlineStr">
         <is>
           <t>Note 9</t>
         </is>
       </c>
-      <c r="B53" s="136" t="inlineStr">
+      <c r="B53" s="137" t="inlineStr">
         <is>
           <t>ADHÉRENTS, CLIENTS-USAGERS</t>
         </is>
@@ -23882,7 +23891,7 @@
       <c r="H53" s="47" t="n"/>
     </row>
     <row r="54" ht="110" customHeight="1">
-      <c r="A54" s="137" t="n"/>
+      <c r="A54" s="138" t="n"/>
       <c r="B54" s="47" t="n"/>
       <c r="C54" s="47" t="n"/>
       <c r="D54" s="47" t="n"/>
@@ -23897,7 +23906,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G55" s="132" t="inlineStr">
+      <c r="G55" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 5/12</t>
@@ -23949,12 +23958,12 @@
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="135" t="inlineStr">
+      <c r="A60" s="136" t="inlineStr">
         <is>
           <t>Note 10</t>
         </is>
       </c>
-      <c r="B60" s="136" t="inlineStr">
+      <c r="B60" s="137" t="inlineStr">
         <is>
           <t>AUTRES CRÉANCES</t>
         </is>
@@ -23967,7 +23976,7 @@
       <c r="H60" s="47" t="n"/>
     </row>
     <row r="61" ht="110" customHeight="1">
-      <c r="A61" s="137" t="n"/>
+      <c r="A61" s="138" t="n"/>
       <c r="B61" s="47" t="n"/>
       <c r="C61" s="47" t="n"/>
       <c r="D61" s="47" t="n"/>
@@ -23977,12 +23986,12 @@
       <c r="H61" s="47" t="n"/>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="135" t="inlineStr">
+      <c r="A62" s="136" t="inlineStr">
         <is>
           <t>Note 11</t>
         </is>
       </c>
-      <c r="B62" s="136" t="inlineStr">
+      <c r="B62" s="137" t="inlineStr">
         <is>
           <t>TITRES DE PLACEMENT</t>
         </is>
@@ -23995,7 +24004,7 @@
       <c r="H62" s="47" t="n"/>
     </row>
     <row r="63" ht="110" customHeight="1">
-      <c r="A63" s="137" t="n"/>
+      <c r="A63" s="138" t="n"/>
       <c r="B63" s="47" t="n"/>
       <c r="C63" s="47" t="n"/>
       <c r="D63" s="47" t="n"/>
@@ -24005,12 +24014,12 @@
       <c r="H63" s="47" t="n"/>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="135" t="inlineStr">
+      <c r="A64" s="136" t="inlineStr">
         <is>
           <t>Note 12</t>
         </is>
       </c>
-      <c r="B64" s="136" t="inlineStr">
+      <c r="B64" s="137" t="inlineStr">
         <is>
           <t>VALEURS À ENCAISSER</t>
         </is>
@@ -24023,7 +24032,7 @@
       <c r="H64" s="47" t="n"/>
     </row>
     <row r="65" ht="110" customHeight="1">
-      <c r="A65" s="137" t="n"/>
+      <c r="A65" s="138" t="n"/>
       <c r="B65" s="47" t="n"/>
       <c r="C65" s="47" t="n"/>
       <c r="D65" s="47" t="n"/>
@@ -24033,12 +24042,12 @@
       <c r="H65" s="47" t="n"/>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="135" t="inlineStr">
+      <c r="A66" s="136" t="inlineStr">
         <is>
           <t>Note 13</t>
         </is>
       </c>
-      <c r="B66" s="136" t="inlineStr">
+      <c r="B66" s="137" t="inlineStr">
         <is>
           <t>DISPONIBILITÉS</t>
         </is>
@@ -24051,7 +24060,7 @@
       <c r="H66" s="47" t="n"/>
     </row>
     <row r="67" ht="110" customHeight="1">
-      <c r="A67" s="137" t="n"/>
+      <c r="A67" s="138" t="n"/>
       <c r="B67" s="47" t="n"/>
       <c r="C67" s="47" t="n"/>
       <c r="D67" s="47" t="n"/>
@@ -24066,7 +24075,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G68" s="132" t="inlineStr">
+      <c r="G68" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 6/12</t>
@@ -24118,12 +24127,12 @@
       </c>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="135" t="inlineStr">
+      <c r="A73" s="136" t="inlineStr">
         <is>
           <t>Note 14</t>
         </is>
       </c>
-      <c r="B73" s="136" t="inlineStr">
+      <c r="B73" s="137" t="inlineStr">
         <is>
           <t>ÉCARTS DE CONVERSION</t>
         </is>
@@ -24136,7 +24145,7 @@
       <c r="H73" s="47" t="n"/>
     </row>
     <row r="74" ht="110" customHeight="1">
-      <c r="A74" s="137" t="n"/>
+      <c r="A74" s="138" t="n"/>
       <c r="B74" s="47" t="n"/>
       <c r="C74" s="47" t="n"/>
       <c r="D74" s="47" t="n"/>
@@ -24146,12 +24155,12 @@
       <c r="H74" s="47" t="n"/>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="135" t="inlineStr">
+      <c r="A75" s="136" t="inlineStr">
         <is>
           <t>Note 15</t>
         </is>
       </c>
-      <c r="B75" s="136" t="inlineStr">
+      <c r="B75" s="137" t="inlineStr">
         <is>
           <t>DOTATION</t>
         </is>
@@ -24164,7 +24173,7 @@
       <c r="H75" s="47" t="n"/>
     </row>
     <row r="76" ht="110" customHeight="1">
-      <c r="A76" s="137" t="n"/>
+      <c r="A76" s="138" t="n"/>
       <c r="B76" s="47" t="n"/>
       <c r="C76" s="47" t="n"/>
       <c r="D76" s="47" t="n"/>
@@ -24174,12 +24183,12 @@
       <c r="H76" s="47" t="n"/>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="135" t="inlineStr">
+      <c r="A77" s="136" t="inlineStr">
         <is>
           <t>Note 16</t>
         </is>
       </c>
-      <c r="B77" s="136" t="inlineStr">
+      <c r="B77" s="137" t="inlineStr">
         <is>
           <t>RÉSERVES</t>
         </is>
@@ -24192,7 +24201,7 @@
       <c r="H77" s="47" t="n"/>
     </row>
     <row r="78" ht="110" customHeight="1">
-      <c r="A78" s="137" t="n"/>
+      <c r="A78" s="138" t="n"/>
       <c r="B78" s="47" t="n"/>
       <c r="C78" s="47" t="n"/>
       <c r="D78" s="47" t="n"/>
@@ -24202,12 +24211,12 @@
       <c r="H78" s="47" t="n"/>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="135" t="inlineStr">
+      <c r="A79" s="136" t="inlineStr">
         <is>
           <t>Note 17A</t>
         </is>
       </c>
-      <c r="B79" s="136" t="inlineStr">
+      <c r="B79" s="137" t="inlineStr">
         <is>
           <t>SUBVENTIONS ET PROVISIONS RÉGLEMENTÉES</t>
         </is>
@@ -24220,7 +24229,7 @@
       <c r="H79" s="47" t="n"/>
     </row>
     <row r="80" ht="110" customHeight="1">
-      <c r="A80" s="137" t="n"/>
+      <c r="A80" s="138" t="n"/>
       <c r="B80" s="47" t="n"/>
       <c r="C80" s="47" t="n"/>
       <c r="D80" s="47" t="n"/>
@@ -24235,7 +24244,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G81" s="132" t="inlineStr">
+      <c r="G81" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 7/12</t>
@@ -24287,12 +24296,12 @@
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="135" t="inlineStr">
+      <c r="A86" s="136" t="inlineStr">
         <is>
           <t>Note 17B</t>
         </is>
       </c>
-      <c r="B86" s="136" t="inlineStr">
+      <c r="B86" s="137" t="inlineStr">
         <is>
           <t>FONDS AFFECTÉS ET REPORTÉS</t>
         </is>
@@ -24305,7 +24314,7 @@
       <c r="H86" s="47" t="n"/>
     </row>
     <row r="87" ht="110" customHeight="1">
-      <c r="A87" s="137" t="n"/>
+      <c r="A87" s="138" t="n"/>
       <c r="B87" s="47" t="n"/>
       <c r="C87" s="47" t="n"/>
       <c r="D87" s="47" t="n"/>
@@ -24315,12 +24324,12 @@
       <c r="H87" s="47" t="n"/>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="135" t="inlineStr">
+      <c r="A88" s="136" t="inlineStr">
         <is>
           <t>Note 18A</t>
         </is>
       </c>
-      <c r="B88" s="136" t="inlineStr">
+      <c r="B88" s="137" t="inlineStr">
         <is>
           <t>DETTES FINANCIÈRES ET RESSOURCES ASSIMILÉES</t>
         </is>
@@ -24333,7 +24342,7 @@
       <c r="H88" s="47" t="n"/>
     </row>
     <row r="89" ht="110" customHeight="1">
-      <c r="A89" s="137" t="n"/>
+      <c r="A89" s="138" t="n"/>
       <c r="B89" s="47" t="n"/>
       <c r="C89" s="47" t="n"/>
       <c r="D89" s="47" t="n"/>
@@ -24343,12 +24352,12 @@
       <c r="H89" s="47" t="n"/>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="135" t="inlineStr">
+      <c r="A90" s="136" t="inlineStr">
         <is>
           <t>Note 18B</t>
         </is>
       </c>
-      <c r="B90" s="136" t="inlineStr">
+      <c r="B90" s="137" t="inlineStr">
         <is>
           <t>ACTIFS ET PASSIFS ÉVENTUELS</t>
         </is>
@@ -24361,7 +24370,7 @@
       <c r="H90" s="47" t="n"/>
     </row>
     <row r="91" ht="110" customHeight="1">
-      <c r="A91" s="137" t="n"/>
+      <c r="A91" s="138" t="n"/>
       <c r="B91" s="47" t="n"/>
       <c r="C91" s="47" t="n"/>
       <c r="D91" s="47" t="n"/>
@@ -24371,12 +24380,12 @@
       <c r="H91" s="47" t="n"/>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="135" t="inlineStr">
+      <c r="A92" s="136" t="inlineStr">
         <is>
           <t>Note 19</t>
         </is>
       </c>
-      <c r="B92" s="136" t="inlineStr">
+      <c r="B92" s="137" t="inlineStr">
         <is>
           <t>FOURNISSEURS D'EXPLOITATION</t>
         </is>
@@ -24389,7 +24398,7 @@
       <c r="H92" s="47" t="n"/>
     </row>
     <row r="93" ht="110" customHeight="1">
-      <c r="A93" s="137" t="n"/>
+      <c r="A93" s="138" t="n"/>
       <c r="B93" s="47" t="n"/>
       <c r="C93" s="47" t="n"/>
       <c r="D93" s="47" t="n"/>
@@ -24404,7 +24413,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G94" s="132" t="inlineStr">
+      <c r="G94" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 8/12</t>
@@ -24456,12 +24465,12 @@
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="135" t="inlineStr">
+      <c r="A99" s="136" t="inlineStr">
         <is>
           <t>Note 20</t>
         </is>
       </c>
-      <c r="B99" s="136" t="inlineStr">
+      <c r="B99" s="137" t="inlineStr">
         <is>
           <t>DETTES FISCALES ET SOCIALES</t>
         </is>
@@ -24474,7 +24483,7 @@
       <c r="H99" s="47" t="n"/>
     </row>
     <row r="100" ht="110" customHeight="1">
-      <c r="A100" s="137" t="n"/>
+      <c r="A100" s="138" t="n"/>
       <c r="B100" s="47" t="n"/>
       <c r="C100" s="47" t="n"/>
       <c r="D100" s="47" t="n"/>
@@ -24484,12 +24493,12 @@
       <c r="H100" s="47" t="n"/>
     </row>
     <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="135" t="inlineStr">
+      <c r="A101" s="136" t="inlineStr">
         <is>
           <t>Note 21</t>
         </is>
       </c>
-      <c r="B101" s="136" t="inlineStr">
+      <c r="B101" s="137" t="inlineStr">
         <is>
           <t>AUTRES DETTES ET PROVISIONS POUR RISQUES ET CHARGES À COURT TERME</t>
         </is>
@@ -24502,7 +24511,7 @@
       <c r="H101" s="47" t="n"/>
     </row>
     <row r="102" ht="110" customHeight="1">
-      <c r="A102" s="137" t="n"/>
+      <c r="A102" s="138" t="n"/>
       <c r="B102" s="47" t="n"/>
       <c r="C102" s="47" t="n"/>
       <c r="D102" s="47" t="n"/>
@@ -24512,12 +24521,12 @@
       <c r="H102" s="47" t="n"/>
     </row>
     <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="135" t="inlineStr">
+      <c r="A103" s="136" t="inlineStr">
         <is>
           <t>Note 22</t>
         </is>
       </c>
-      <c r="B103" s="136" t="inlineStr">
+      <c r="B103" s="137" t="inlineStr">
         <is>
           <t>BANQUES, CRÉDIT D'ESCOMPTE ET DE TRÉSORERIE</t>
         </is>
@@ -24530,7 +24539,7 @@
       <c r="H103" s="47" t="n"/>
     </row>
     <row r="104" ht="110" customHeight="1">
-      <c r="A104" s="137" t="n"/>
+      <c r="A104" s="138" t="n"/>
       <c r="B104" s="47" t="n"/>
       <c r="C104" s="47" t="n"/>
       <c r="D104" s="47" t="n"/>
@@ -24540,26 +24549,26 @@
       <c r="H104" s="47" t="n"/>
     </row>
     <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="133" t="inlineStr">
+      <c r="A105" s="134" t="inlineStr">
         <is>
           <t>Partie 3 : Notes sur le compte de résultat</t>
         </is>
       </c>
-      <c r="B105" s="134" t="n"/>
-      <c r="C105" s="134" t="n"/>
-      <c r="D105" s="134" t="n"/>
-      <c r="E105" s="134" t="n"/>
-      <c r="F105" s="134" t="n"/>
-      <c r="G105" s="134" t="n"/>
-      <c r="H105" s="134" t="n"/>
+      <c r="B105" s="135" t="n"/>
+      <c r="C105" s="135" t="n"/>
+      <c r="D105" s="135" t="n"/>
+      <c r="E105" s="135" t="n"/>
+      <c r="F105" s="135" t="n"/>
+      <c r="G105" s="135" t="n"/>
+      <c r="H105" s="135" t="n"/>
     </row>
     <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="135" t="inlineStr">
+      <c r="A106" s="136" t="inlineStr">
         <is>
           <t>Note 23</t>
         </is>
       </c>
-      <c r="B106" s="136" t="inlineStr">
+      <c r="B106" s="137" t="inlineStr">
         <is>
           <t>REVENUS ET AUTRES PRODUITS</t>
         </is>
@@ -24572,7 +24581,7 @@
       <c r="H106" s="47" t="n"/>
     </row>
     <row r="107" ht="110" customHeight="1">
-      <c r="A107" s="137" t="n"/>
+      <c r="A107" s="138" t="n"/>
       <c r="B107" s="47" t="n"/>
       <c r="C107" s="47" t="n"/>
       <c r="D107" s="47" t="n"/>
@@ -24587,7 +24596,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G108" s="132" t="inlineStr">
+      <c r="G108" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 9/12</t>
@@ -24639,12 +24648,12 @@
       </c>
     </row>
     <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="135" t="inlineStr">
+      <c r="A113" s="136" t="inlineStr">
         <is>
           <t>Note 24</t>
         </is>
       </c>
-      <c r="B113" s="136" t="inlineStr">
+      <c r="B113" s="137" t="inlineStr">
         <is>
           <t>ACHATS</t>
         </is>
@@ -24657,7 +24666,7 @@
       <c r="H113" s="47" t="n"/>
     </row>
     <row r="114" ht="110" customHeight="1">
-      <c r="A114" s="137" t="n"/>
+      <c r="A114" s="138" t="n"/>
       <c r="B114" s="47" t="n"/>
       <c r="C114" s="47" t="n"/>
       <c r="D114" s="47" t="n"/>
@@ -24667,12 +24676,12 @@
       <c r="H114" s="47" t="n"/>
     </row>
     <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="135" t="inlineStr">
+      <c r="A115" s="136" t="inlineStr">
         <is>
           <t>Note 25</t>
         </is>
       </c>
-      <c r="B115" s="136" t="inlineStr">
+      <c r="B115" s="137" t="inlineStr">
         <is>
           <t>TRANSPORTS</t>
         </is>
@@ -24685,7 +24694,7 @@
       <c r="H115" s="47" t="n"/>
     </row>
     <row r="116" ht="110" customHeight="1">
-      <c r="A116" s="137" t="n"/>
+      <c r="A116" s="138" t="n"/>
       <c r="B116" s="47" t="n"/>
       <c r="C116" s="47" t="n"/>
       <c r="D116" s="47" t="n"/>
@@ -24695,12 +24704,12 @@
       <c r="H116" s="47" t="n"/>
     </row>
     <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="135" t="inlineStr">
+      <c r="A117" s="136" t="inlineStr">
         <is>
           <t>Note 26</t>
         </is>
       </c>
-      <c r="B117" s="136" t="inlineStr">
+      <c r="B117" s="137" t="inlineStr">
         <is>
           <t>SERVICES EXTÉRIEURS</t>
         </is>
@@ -24713,7 +24722,7 @@
       <c r="H117" s="47" t="n"/>
     </row>
     <row r="118" ht="110" customHeight="1">
-      <c r="A118" s="137" t="n"/>
+      <c r="A118" s="138" t="n"/>
       <c r="B118" s="47" t="n"/>
       <c r="C118" s="47" t="n"/>
       <c r="D118" s="47" t="n"/>
@@ -24723,12 +24732,12 @@
       <c r="H118" s="47" t="n"/>
     </row>
     <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="135" t="inlineStr">
+      <c r="A119" s="136" t="inlineStr">
         <is>
           <t>Note 27</t>
         </is>
       </c>
-      <c r="B119" s="136" t="inlineStr">
+      <c r="B119" s="137" t="inlineStr">
         <is>
           <t>IMPÔTS ET TAXES</t>
         </is>
@@ -24741,7 +24750,7 @@
       <c r="H119" s="47" t="n"/>
     </row>
     <row r="120" ht="110" customHeight="1">
-      <c r="A120" s="137" t="n"/>
+      <c r="A120" s="138" t="n"/>
       <c r="B120" s="47" t="n"/>
       <c r="C120" s="47" t="n"/>
       <c r="D120" s="47" t="n"/>
@@ -24756,7 +24765,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G121" s="132" t="inlineStr">
+      <c r="G121" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 10/12</t>
@@ -24808,12 +24817,12 @@
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="135" t="inlineStr">
+      <c r="A126" s="136" t="inlineStr">
         <is>
           <t>Note 28</t>
         </is>
       </c>
-      <c r="B126" s="136" t="inlineStr">
+      <c r="B126" s="137" t="inlineStr">
         <is>
           <t>AUTRES CHARGES</t>
         </is>
@@ -24826,7 +24835,7 @@
       <c r="H126" s="47" t="n"/>
     </row>
     <row r="127" ht="110" customHeight="1">
-      <c r="A127" s="137" t="n"/>
+      <c r="A127" s="138" t="n"/>
       <c r="B127" s="47" t="n"/>
       <c r="C127" s="47" t="n"/>
       <c r="D127" s="47" t="n"/>
@@ -24836,12 +24845,12 @@
       <c r="H127" s="47" t="n"/>
     </row>
     <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="135" t="inlineStr">
+      <c r="A128" s="136" t="inlineStr">
         <is>
           <t>Note 29A</t>
         </is>
       </c>
-      <c r="B128" s="136" t="inlineStr">
+      <c r="B128" s="137" t="inlineStr">
         <is>
           <t>CHARGES DE PERSONNEL</t>
         </is>
@@ -24854,7 +24863,7 @@
       <c r="H128" s="47" t="n"/>
     </row>
     <row r="129" ht="110" customHeight="1">
-      <c r="A129" s="137" t="n"/>
+      <c r="A129" s="138" t="n"/>
       <c r="B129" s="47" t="n"/>
       <c r="C129" s="47" t="n"/>
       <c r="D129" s="47" t="n"/>
@@ -24864,12 +24873,12 @@
       <c r="H129" s="47" t="n"/>
     </row>
     <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="135" t="inlineStr">
+      <c r="A130" s="136" t="inlineStr">
         <is>
           <t>Note 29B</t>
         </is>
       </c>
-      <c r="B130" s="136" t="inlineStr">
+      <c r="B130" s="137" t="inlineStr">
         <is>
           <t>EFFECTIFS, MASSE SALARIALE ET PERSONNEL EXTÉRIEUR</t>
         </is>
@@ -24882,7 +24891,7 @@
       <c r="H130" s="47" t="n"/>
     </row>
     <row r="131" ht="110" customHeight="1">
-      <c r="A131" s="137" t="n"/>
+      <c r="A131" s="138" t="n"/>
       <c r="B131" s="47" t="n"/>
       <c r="C131" s="47" t="n"/>
       <c r="D131" s="47" t="n"/>
@@ -24892,12 +24901,12 @@
       <c r="H131" s="47" t="n"/>
     </row>
     <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="135" t="inlineStr">
+      <c r="A132" s="136" t="inlineStr">
         <is>
           <t>Note 30</t>
         </is>
       </c>
-      <c r="B132" s="136" t="inlineStr">
+      <c r="B132" s="137" t="inlineStr">
         <is>
           <t>DOTATIONS ET CHARGES POUR PROVISIONS ET DÉPRÉCIATIONS</t>
         </is>
@@ -24910,7 +24919,7 @@
       <c r="H132" s="47" t="n"/>
     </row>
     <row r="133" ht="110" customHeight="1">
-      <c r="A133" s="137" t="n"/>
+      <c r="A133" s="138" t="n"/>
       <c r="B133" s="47" t="n"/>
       <c r="C133" s="47" t="n"/>
       <c r="D133" s="47" t="n"/>
@@ -24925,7 +24934,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G134" s="132" t="inlineStr">
+      <c r="G134" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 11/12</t>
@@ -24977,12 +24986,12 @@
       </c>
     </row>
     <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="135" t="inlineStr">
+      <c r="A139" s="136" t="inlineStr">
         <is>
           <t>Note 31</t>
         </is>
       </c>
-      <c r="B139" s="136" t="inlineStr">
+      <c r="B139" s="137" t="inlineStr">
         <is>
           <t>CHARGES ET REVENUS FINANCIERS</t>
         </is>
@@ -24995,7 +25004,7 @@
       <c r="H139" s="47" t="n"/>
     </row>
     <row r="140" ht="110" customHeight="1">
-      <c r="A140" s="137" t="n"/>
+      <c r="A140" s="138" t="n"/>
       <c r="B140" s="47" t="n"/>
       <c r="C140" s="47" t="n"/>
       <c r="D140" s="47" t="n"/>
@@ -25005,12 +25014,12 @@
       <c r="H140" s="47" t="n"/>
     </row>
     <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="135" t="inlineStr">
+      <c r="A141" s="136" t="inlineStr">
         <is>
           <t>Note 32</t>
         </is>
       </c>
-      <c r="B141" s="136" t="inlineStr">
+      <c r="B141" s="137" t="inlineStr">
         <is>
           <t>AUTRES CHARGES ET PRODUITS HAO</t>
         </is>
@@ -25023,7 +25032,7 @@
       <c r="H141" s="47" t="n"/>
     </row>
     <row r="142" ht="110" customHeight="1">
-      <c r="A142" s="137" t="n"/>
+      <c r="A142" s="138" t="n"/>
       <c r="B142" s="47" t="n"/>
       <c r="C142" s="47" t="n"/>
       <c r="D142" s="47" t="n"/>
@@ -25033,26 +25042,26 @@
       <c r="H142" s="47" t="n"/>
     </row>
     <row r="143" ht="17" customHeight="1">
-      <c r="A143" s="133" t="inlineStr">
+      <c r="A143" s="134" t="inlineStr">
         <is>
           <t>Partie 4 : Autres informations</t>
         </is>
       </c>
-      <c r="B143" s="134" t="n"/>
-      <c r="C143" s="134" t="n"/>
-      <c r="D143" s="134" t="n"/>
-      <c r="E143" s="134" t="n"/>
-      <c r="F143" s="134" t="n"/>
-      <c r="G143" s="134" t="n"/>
-      <c r="H143" s="134" t="n"/>
+      <c r="B143" s="135" t="n"/>
+      <c r="C143" s="135" t="n"/>
+      <c r="D143" s="135" t="n"/>
+      <c r="E143" s="135" t="n"/>
+      <c r="F143" s="135" t="n"/>
+      <c r="G143" s="135" t="n"/>
+      <c r="H143" s="135" t="n"/>
     </row>
     <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="135" t="inlineStr">
+      <c r="A144" s="136" t="inlineStr">
         <is>
           <t>Note 33</t>
         </is>
       </c>
-      <c r="B144" s="136" t="inlineStr">
+      <c r="B144" s="137" t="inlineStr">
         <is>
           <t>FICHE DE SYNTHÈSE DES PRINCIPAUX INDICATEURS FINANCIERS</t>
         </is>
@@ -25065,7 +25074,7 @@
       <c r="H144" s="47" t="n"/>
     </row>
     <row r="145" ht="110" customHeight="1">
-      <c r="A145" s="137" t="n"/>
+      <c r="A145" s="138" t="n"/>
       <c r="B145" s="47" t="n"/>
       <c r="C145" s="47" t="n"/>
       <c r="D145" s="47" t="n"/>
@@ -25075,12 +25084,12 @@
       <c r="H145" s="47" t="n"/>
     </row>
     <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="135" t="inlineStr">
+      <c r="A146" s="136" t="inlineStr">
         <is>
           <t>Note 34</t>
         </is>
       </c>
-      <c r="B146" s="136" t="inlineStr">
+      <c r="B146" s="137" t="inlineStr">
         <is>
           <t>LISTE DES INFORMATIONS SOCIALES, ENVIRONNEMENTALES ET SOCIÉTALES</t>
         </is>
@@ -25093,7 +25102,7 @@
       <c r="H146" s="47" t="n"/>
     </row>
     <row r="147" ht="110" customHeight="1">
-      <c r="A147" s="137" t="n"/>
+      <c r="A147" s="138" t="n"/>
       <c r="B147" s="47" t="n"/>
       <c r="C147" s="47" t="n"/>
       <c r="D147" s="47" t="n"/>
@@ -25108,7 +25117,7 @@
           <t>TABLE DES COMMENTAIRES</t>
         </is>
       </c>
-      <c r="G148" s="132" t="inlineStr">
+      <c r="G148" s="133" t="inlineStr">
         <is>
           <t>COMMENTAIRES
 PAGE 12/12</t>
@@ -25160,12 +25169,12 @@
       </c>
     </row>
     <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="135" t="inlineStr">
+      <c r="A153" s="136" t="inlineStr">
         <is>
           <t>Note 35</t>
         </is>
       </c>
-      <c r="B153" s="136" t="inlineStr">
+      <c r="B153" s="137" t="inlineStr">
         <is>
           <t>TABLEAU D'EXÉCUTION BUDGÉTAIRE</t>
         </is>
@@ -25178,7 +25187,7 @@
       <c r="H153" s="47" t="n"/>
     </row>
     <row r="154" ht="110" customHeight="1">
-      <c r="A154" s="137" t="n"/>
+      <c r="A154" s="138" t="n"/>
       <c r="B154" s="47" t="n"/>
       <c r="C154" s="47" t="n"/>
       <c r="D154" s="47" t="n"/>
@@ -28812,7 +28821,7 @@
       </c>
       <c r="C12" s="90" t="inlineStr"/>
       <c r="D12" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E12" s="80">
@@ -28824,7 +28833,7 @@
         <v/>
       </c>
       <c r="G12" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2902*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2902*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2902*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2902*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -28878,11 +28887,11 @@
         </is>
       </c>
       <c r="D14" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E14" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F14" s="80">
@@ -28890,7 +28899,7 @@
         <v/>
       </c>
       <c r="G14" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -28911,7 +28920,7 @@
         <v/>
       </c>
       <c r="E15" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2818*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2818*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2918*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2918*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2918*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2918*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2818*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2818*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F15" s="80">
@@ -28919,7 +28928,7 @@
         <v/>
       </c>
       <c r="G15" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2818*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2818*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2918*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2918*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2918*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2918*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2818*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2818*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29026,11 +29035,11 @@
       </c>
       <c r="C19" s="90" t="inlineStr"/>
       <c r="D19" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E19" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F19" s="80">
@@ -29038,7 +29047,7 @@
         <v/>
       </c>
       <c r="G19" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29059,7 +29068,7 @@
         <v/>
       </c>
       <c r="E20" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F20" s="80">
@@ -29067,7 +29076,7 @@
         <v/>
       </c>
       <c r="G20" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29088,7 +29097,7 @@
         <v/>
       </c>
       <c r="E21" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F21" s="80">
@@ -29096,7 +29105,7 @@
         <v/>
       </c>
       <c r="G21" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29117,7 +29126,7 @@
         <v/>
       </c>
       <c r="E22" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F22" s="80">
@@ -29125,7 +29134,7 @@
         <v/>
       </c>
       <c r="G22" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29328,7 +29337,7 @@
         </is>
       </c>
       <c r="D29" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E29" s="80">
@@ -29340,7 +29349,7 @@
         <v/>
       </c>
       <c r="G29" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29427,11 +29436,11 @@
         </is>
       </c>
       <c r="D32" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"478*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"478*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E32" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F32" s="80">
@@ -29439,7 +29448,7 @@
         <v/>
       </c>
       <c r="G32" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"478*",'BALANCE N-1'!$G$2:$G$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"478*",'BALANCE N-1'!$G$2:$G$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29555,11 +29564,11 @@
         </is>
       </c>
       <c r="D36" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E36" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F36" s="80">
@@ -29567,7 +29576,7 @@
         <v/>
       </c>
       <c r="G36" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>

--- a/.claude/skills/sycebnl/liasse/assets/gabarit-etats-associations.xlsx
+++ b/.claude/skills/sycebnl/liasse/assets/gabarit-etats-associations.xlsx
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="D25" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2089,11 +2089,11 @@
         </is>
       </c>
       <c r="D30" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2164,11 +2164,11 @@
         </is>
       </c>
       <c r="D33" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"599*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"499*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"479*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"499*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"599*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"479*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"599*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"499*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"479*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"499*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"599*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"479*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000))</f>
         <v/>
       </c>
     </row>
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="D14" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"7053*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"7053*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"7052*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"7052*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"7052*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"7052*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"7053*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"7053*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E14" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"7053*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"7053*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"7052*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"7052*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"7052*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"7052*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"7053*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"7053*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2594,11 +2594,11 @@
         </is>
       </c>
       <c r="D16" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E16" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2740,11 +2740,11 @@
         </is>
       </c>
       <c r="D22" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E22" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2765,11 +2765,11 @@
         </is>
       </c>
       <c r="D23" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E23" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2815,11 +2815,11 @@
         </is>
       </c>
       <c r="D25" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"63*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"63*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"62*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"62*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"62*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"62*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"63*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"63*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"63*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"63*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"62*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"62*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"62*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"62*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"63*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"63*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="D33" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="D34" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E34" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="D9" s="101">
-        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)))))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$G$2:$G$2000))+(SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)))))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$G$2:$G$2000))+(SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E9" s="102" t="n"/>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="D25" s="84">
-        <f>-((((SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$H$2:$H$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$H$2:$H$2000)))))</f>
+        <f>-((((SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$H$2:$H$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$H$2:$H$2000)))))</f>
         <v/>
       </c>
       <c r="E25" s="85" t="n"/>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="D34" s="7">
-        <f>(((SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$G$2:$G$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$G$2:$G$2000))))</f>
+        <f>(((SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$G$2:$G$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$G$2:$G$2000))))</f>
         <v/>
       </c>
       <c r="E34" s="82" t="n"/>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D35" s="101">
-        <f>(((((SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)))))-((SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$G$2:$G$2000))+(SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000))))-D9</f>
+        <f>(((((SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)))))-((SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$G$2:$G$2000))+(SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000))))-D9</f>
         <v/>
       </c>
       <c r="E35" s="102" t="n"/>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B13" s="119" t="inlineStr"/>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D13" s="120" t="n"/>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="B17" s="119" t="inlineStr"/>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="C26" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"479*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"478*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"478*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"479*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D26" s="120" t="n"/>
@@ -6088,15 +6088,15 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E11" s="120">
@@ -6111,15 +6111,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -6420,15 +6420,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -6569,15 +6569,15 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E17" s="120">
@@ -6592,15 +6592,15 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D18" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E18" s="120">
@@ -6615,15 +6615,15 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E19" s="120">
@@ -7093,15 +7093,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -7519,15 +7519,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -7645,15 +7645,15 @@
         </is>
       </c>
       <c r="B16" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D16" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="E16" s="120">
@@ -9377,11 +9377,11 @@
         </is>
       </c>
       <c r="B21" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4881*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4881*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4881*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4881*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C21" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4881*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4881*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4881*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4881*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D21" s="120">
@@ -10838,11 +10838,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"471*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"472*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"475*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"475*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"471*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"472*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"471*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"472*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"475*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"475*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"471*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"472*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -10864,11 +10864,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -10916,11 +10916,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -11903,11 +11903,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"524*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"523*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"523*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"524*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"524*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"523*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"523*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"524*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -11972,11 +11972,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"532*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"533*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"538*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"538*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"532*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"533*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"532*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"533*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"538*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"538*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"532*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"533*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -12087,11 +12087,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -13489,11 +13489,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -14171,11 +14171,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -15018,11 +15018,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -15518,11 +15518,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"427*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"425*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"424*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"428*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"421*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"423*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4281*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"428*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"423*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"425*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"424*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"427*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"421*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4281*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"427*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"425*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"424*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"428*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"421*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"423*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4281*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"428*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"423*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"425*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"424*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"427*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"421*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4281*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -15700,11 +15700,11 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"442*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"446*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"446*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"442*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"442*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"446*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"442*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D19" s="120">
@@ -15726,11 +15726,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"444*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"445*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"443*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"444*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"443*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"445*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"444*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"445*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"443*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"444*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"443*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"445*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -16141,11 +16141,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4712*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4717*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4719*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4711*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4712*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4719*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4711*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4717*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4712*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4717*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4719*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4711*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4712*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4719*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4711*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4717*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -16245,11 +16245,11 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4721*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4721*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4721*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4721*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D18" s="120">
@@ -16554,11 +16554,11 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"525*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"524*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"523*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"523*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"525*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"524*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"525*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"524*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"523*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"523*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"525*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"524*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D11" s="120">
@@ -16909,11 +16909,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -16978,11 +16978,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -20333,17 +20333,17 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
       <c r="E17" s="120" t="n"/>
       <c r="F17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="G17" s="120" t="n"/>
@@ -22109,11 +22109,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -28821,7 +28821,7 @@
       </c>
       <c r="C12" s="90" t="inlineStr"/>
       <c r="D12" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E12" s="80">
@@ -28833,7 +28833,7 @@
         <v/>
       </c>
       <c r="G12" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2902*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2902*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2902*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2902*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -28887,11 +28887,11 @@
         </is>
       </c>
       <c r="D14" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E14" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F14" s="80">
@@ -28899,7 +28899,7 @@
         <v/>
       </c>
       <c r="G14" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -28920,7 +28920,7 @@
         <v/>
       </c>
       <c r="E15" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2918*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2918*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2818*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2818*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2818*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2818*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2918*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2918*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F15" s="80">
@@ -28928,7 +28928,7 @@
         <v/>
       </c>
       <c r="G15" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2918*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2918*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2818*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2818*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2818*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2818*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2918*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2918*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29010,7 +29010,7 @@
         <v/>
       </c>
       <c r="E18" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"282*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"282*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"292*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"292*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"292*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"292*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"282*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"282*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F18" s="80">
@@ -29018,7 +29018,7 @@
         <v/>
       </c>
       <c r="G18" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"282*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"282*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"292*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"292*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"292*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"292*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"282*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"282*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29035,11 +29035,11 @@
       </c>
       <c r="C19" s="90" t="inlineStr"/>
       <c r="D19" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E19" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F19" s="80">
@@ -29047,7 +29047,7 @@
         <v/>
       </c>
       <c r="G19" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29064,11 +29064,11 @@
       </c>
       <c r="C20" s="90" t="inlineStr"/>
       <c r="D20" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E20" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F20" s="80">
@@ -29076,7 +29076,7 @@
         <v/>
       </c>
       <c r="G20" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29097,7 +29097,7 @@
         <v/>
       </c>
       <c r="E21" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F21" s="80">
@@ -29105,7 +29105,7 @@
         <v/>
       </c>
       <c r="G21" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29126,7 +29126,7 @@
         <v/>
       </c>
       <c r="E22" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F22" s="80">
@@ -29134,7 +29134,7 @@
         <v/>
       </c>
       <c r="G22" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29337,7 +29337,7 @@
         </is>
       </c>
       <c r="D29" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E29" s="80">
@@ -29349,7 +29349,7 @@
         <v/>
       </c>
       <c r="G29" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29436,11 +29436,11 @@
         </is>
       </c>
       <c r="D32" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"478*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"478*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E32" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F32" s="80">
@@ -29448,7 +29448,7 @@
         <v/>
       </c>
       <c r="G32" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"478*",'BALANCE N-1'!$G$2:$G$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"478*",'BALANCE N-1'!$G$2:$G$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29568,7 +29568,7 @@
         <v/>
       </c>
       <c r="E36" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F36" s="80">
@@ -29576,7 +29576,7 @@
         <v/>
       </c>
       <c r="G36" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>

--- a/.claude/skills/sycebnl/liasse/assets/gabarit-etats-associations.xlsx
+++ b/.claude/skills/sycebnl/liasse/assets/gabarit-etats-associations.xlsx
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="D25" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E25" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2089,11 +2089,11 @@
         </is>
       </c>
       <c r="D30" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"481*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"484*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"488*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4861*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"481*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"484*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"488*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4861*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2164,11 +2164,11 @@
         </is>
       </c>
       <c r="D33" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"499*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"599*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"479*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"499*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"599*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"479*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4998*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"499*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"599*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"479*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"499*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"599*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"479*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4998*",'BALANCE N-1'!$H$2:$H$2000))</f>
         <v/>
       </c>
     </row>
@@ -2594,11 +2594,11 @@
         </is>
       </c>
       <c r="D16" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"706*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E16" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"706*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2740,11 +2740,11 @@
         </is>
       </c>
       <c r="D22" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"604*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"605*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"606*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"608*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E22" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"604*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"605*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"606*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"608*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2765,11 +2765,11 @@
         </is>
       </c>
       <c r="D23" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6032*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6033*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6034*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"6035*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E23" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6032*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6033*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6034*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"6035*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -2940,11 +2940,11 @@
         </is>
       </c>
       <c r="D30" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E30" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -3007,11 +3007,11 @@
         </is>
       </c>
       <c r="D33" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"84*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"88*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E33" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"84*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"88*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="D34" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"83*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"87*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E34" s="81">
-        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"83*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"87*",'BALANCE N-1'!$G$2:$G$2000))</f>
         <v/>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="D9" s="101">
-        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)))))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$G$2:$G$2000))+(SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>((((SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"50*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"590*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"51*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"591*",'BALANCE N-1'!$G$2:$G$2000))))+(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)))))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"564*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"565*",'BALANCE N-1'!$G$2:$G$2000))+(SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E9" s="102" t="n"/>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="D25" s="84">
-        <f>-((((SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$H$2:$H$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$H$2:$H$2000)))))</f>
+        <f>-((((SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"201*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"202*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"203*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"204*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"205*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2198*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"251*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"22*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"24*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"245*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2495*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"252*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"26*",'BALANCE N'!$H$2:$H$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"27*",'BALANCE N'!$H$2:$H$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"201*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"202*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"203*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"204*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"205*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2198*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"251*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"252*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"26*",'BALANCE N-1'!$H$2:$H$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"27*",'BALANCE N-1'!$H$2:$H$2000)))))</f>
         <v/>
       </c>
       <c r="E25" s="85" t="n"/>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="D34" s="7">
-        <f>(((SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$G$2:$G$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$G$2:$G$2000))))</f>
+        <f>(((SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"181*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"182*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)))+((SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"19*",'BALANCE N'!$G$2:$G$2000))))-(((SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"181*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"182*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"183*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"185*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"186*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"188*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)))+((SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"19*",'BALANCE N-1'!$G$2:$G$2000))))</f>
         <v/>
       </c>
       <c r="E34" s="82" t="n"/>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="D35" s="101">
-        <f>(((((SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)))))-((SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$G$2:$G$2000))+(SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000))))-D9</f>
+        <f>(((((SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"50*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"590*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"51*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"591*",'BALANCE N'!$G$2:$G$2000))))+(((SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)))-((SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)))))-((SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"564*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"565*",'BALANCE N'!$G$2:$G$2000))+(SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000))))-D9</f>
         <v/>
       </c>
       <c r="E35" s="102" t="n"/>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B13" s="119" t="inlineStr"/>
       <c r="C13" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"183*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"185*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"186*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"188*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D13" s="120" t="n"/>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="B17" s="119" t="inlineStr"/>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
@@ -6088,15 +6088,15 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D11" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2012*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2013*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2012*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2013*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E11" s="120">
@@ -6111,15 +6111,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2014*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2017*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2014*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2017*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -6420,15 +6420,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"218*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"218*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -6569,15 +6569,15 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2315*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2325*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2315*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2325*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E17" s="120">
@@ -6615,15 +6615,15 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D19" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E19" s="120">
@@ -7093,15 +7093,15 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="D12" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2416*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2426*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2446*",'BALANCE N-1'!$H$2:$H$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2416*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2426*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2446*",'BALANCE N'!$H$2:$H$2000)))</f>
         <v/>
       </c>
       <c r="E12" s="120">
@@ -7519,15 +7519,15 @@
         </is>
       </c>
       <c r="B10" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D10" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2817*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2817*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="E10" s="120">
@@ -7622,15 +7622,15 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D15" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="E15" s="120">
@@ -10838,11 +10838,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"475*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"471*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"472*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"471*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"472*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"475*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"475*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"471*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"472*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"471*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"472*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"475*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -10864,11 +10864,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -10916,11 +10916,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -11972,11 +11972,11 @@
         </is>
       </c>
       <c r="B15" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"538*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"532*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"533*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"532*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"533*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"538*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C15" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"538*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"532*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"533*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"532*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"533*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"538*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D15" s="120">
@@ -12087,11 +12087,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -12516,11 +12516,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"102*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"102*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"101*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"101*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"101*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"101*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"102*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"102*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"102*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"102*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"101*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"101*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"101*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"101*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"102*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"102*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -13489,11 +13489,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"161*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"162*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"163*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"164*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"161*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"162*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"163*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"164*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -13558,11 +13558,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"169*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"169*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"168*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"168*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"168*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"168*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"169*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"169*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"169*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"169*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"168*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"168*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"168*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"168*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"169*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"169*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -14171,11 +14171,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"187*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1871*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1872*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1873*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"1876*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"187*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1871*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1872*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1873*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"1876*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -15018,11 +15018,11 @@
         </is>
       </c>
       <c r="B9" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4011*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4013*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C9" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4011*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4013*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D9" s="120">
@@ -15236,11 +15236,11 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4098*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4094*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4094*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4098*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4098*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4094*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4094*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4098*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D18" s="120">
@@ -15518,11 +15518,11 @@
         </is>
       </c>
       <c r="B12" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"428*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"423*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"425*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"424*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"427*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"421*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4281*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"421*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"423*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"424*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"425*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"427*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"428*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"4281*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C12" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"428*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"423*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"425*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"424*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"427*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"421*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4281*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"421*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"423*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"424*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"425*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"427*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"428*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"4281*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D12" s="120">
@@ -15700,11 +15700,11 @@
         </is>
       </c>
       <c r="B19" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"446*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"442*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"442*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"446*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C19" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"446*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"442*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"442*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"446*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D19" s="120">
@@ -15726,11 +15726,11 @@
         </is>
       </c>
       <c r="B20" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"444*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"443*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"445*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"443*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"444*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"445*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C20" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"444*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"443*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"445*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"443*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"444*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"445*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D20" s="120">
@@ -16141,11 +16141,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4712*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4719*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4711*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4717*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"4711*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4712*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4717*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4719*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4712*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4719*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4711*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4717*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"4711*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4712*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4717*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4719*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -16245,11 +16245,11 @@
         </is>
       </c>
       <c r="B18" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4721*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"473*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"474*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"476*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"477*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"4721*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C18" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4721*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"473*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"474*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"476*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"477*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"4721*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D18" s="120">
@@ -16554,11 +16554,11 @@
         </is>
       </c>
       <c r="B11" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"523*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"525*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"524*",'BALANCE N'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"523*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"524*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"525*",'BALANCE N'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="C11" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"523*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"525*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"524*",'BALANCE N-1'!$H$2:$H$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"523*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"524*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"525*",'BALANCE N-1'!$H$2:$H$2000)</f>
         <v/>
       </c>
       <c r="D11" s="120">
@@ -16909,11 +16909,11 @@
         </is>
       </c>
       <c r="B14" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"702*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"707*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"708*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C14" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"702*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"707*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"708*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D14" s="120">
@@ -16978,11 +16978,11 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"72*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"73*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"75*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"77*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"78*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"72*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"73*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"75*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"77*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"78*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D17" s="120">
@@ -20333,17 +20333,17 @@
         </is>
       </c>
       <c r="B17" s="120">
-        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000))-(SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="D17" s="120" t="n"/>
       <c r="E17" s="120" t="n"/>
       <c r="F17" s="120">
-        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)))</f>
+        <f>MAX(0,(SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000))-(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)))</f>
         <v/>
       </c>
       <c r="G17" s="120" t="n"/>
@@ -22109,11 +22109,11 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)</f>
+        <f>'Résultat'!D36+SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"68*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"69*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"85*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"79*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"86*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"81*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"82*",'BALANCE N'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="C13" s="120">
-        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)</f>
+        <f>'Résultat'!E36+SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"68*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"69*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"85*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"79*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"86*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"81*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"82*",'BALANCE N-1'!$G$2:$G$2000)</f>
         <v/>
       </c>
       <c r="D13" s="120">
@@ -28887,11 +28887,11 @@
         </is>
       </c>
       <c r="D14" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"212*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"213*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"214*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2193*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E14" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2812*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2813*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2814*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2912*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2913*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2919*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F14" s="80">
@@ -28899,7 +28899,7 @@
         <v/>
       </c>
       <c r="G14" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"212*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"213*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"214*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2193*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2812*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2813*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2814*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2912*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2913*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2919*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29010,7 +29010,7 @@
         <v/>
       </c>
       <c r="E18" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"292*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"292*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"282*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"282*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"282*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"282*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"292*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"292*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F18" s="80">
@@ -29018,7 +29018,7 @@
         <v/>
       </c>
       <c r="G18" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"292*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"292*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"282*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"282*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"22*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"282*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"282*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"292*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"292*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29035,11 +29035,11 @@
       </c>
       <c r="C19" s="90" t="inlineStr"/>
       <c r="D19" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"231*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"232*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"233*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2391*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2392*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2393*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2396*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E19" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2831*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2832*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2833*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2931*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2932*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2933*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F19" s="80">
@@ -29047,7 +29047,7 @@
         <v/>
       </c>
       <c r="G19" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"231*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"232*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"233*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2391*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2392*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2393*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2396*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2831*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2832*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2833*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2931*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2932*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2933*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29064,11 +29064,11 @@
       </c>
       <c r="C20" s="90" t="inlineStr"/>
       <c r="D20" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"234*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"235*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"238*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2394*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2395*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2398*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E20" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2834*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2835*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2838*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2934*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2935*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2938*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2939*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F20" s="80">
@@ -29076,7 +29076,7 @@
         <v/>
       </c>
       <c r="G20" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"234*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"235*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"238*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2394*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2395*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2398*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2834*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2835*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2838*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2934*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2935*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2938*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2939*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29097,7 +29097,7 @@
         <v/>
       </c>
       <c r="E21" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"284*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"294*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F21" s="80">
@@ -29105,7 +29105,7 @@
         <v/>
       </c>
       <c r="G21" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"24*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"284*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"294*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29126,7 +29126,7 @@
         <v/>
       </c>
       <c r="E22" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2845*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2945*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"2949*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F22" s="80">
@@ -29134,7 +29134,7 @@
         <v/>
       </c>
       <c r="G22" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"245*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2495*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2845*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2945*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"2949*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29337,7 +29337,7 @@
         </is>
       </c>
       <c r="D29" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"31*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"32*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"33*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"34*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"36*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"37*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"38*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E29" s="80">
@@ -29349,7 +29349,7 @@
         <v/>
       </c>
       <c r="G29" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"31*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"32*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"33*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"34*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"36*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"37*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"38*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"39*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29436,11 +29436,11 @@
         </is>
       </c>
       <c r="D32" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"478*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"42*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"43*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"44*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"45*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"46*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"47*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"478*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="E32" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"492*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"493*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"494*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"497*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F32" s="80">
@@ -29448,7 +29448,7 @@
         <v/>
       </c>
       <c r="G32" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"478*",'BALANCE N-1'!$G$2:$G$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"42*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"43*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"44*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"45*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"46*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"47*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"478*",'BALANCE N-1'!$G$2:$G$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"492*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"493*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"494*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"497*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
@@ -29564,11 +29564,11 @@
         </is>
       </c>
       <c r="D36" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"52*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"53*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"55*",'BALANCE N'!$H$2:$H$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$G$2:$G$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"57*",'BALANCE N'!$H$2:$H$2000))</f>
         <v/>
       </c>
       <c r="E36" s="80">
-        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000))</f>
+        <f>(SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"592*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"593*",'BALANCE N'!$G$2:$G$2000)+SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$H$2:$H$2000)-SUMIF('BALANCE N'!$A$2:$A$2000,"595*",'BALANCE N'!$G$2:$G$2000))</f>
         <v/>
       </c>
       <c r="F36" s="80">
@@ -29576,7 +29576,7 @@
         <v/>
       </c>
       <c r="G36" s="81">
-        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)))</f>
+        <f>((SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"52*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"53*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"55*",'BALANCE N-1'!$H$2:$H$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$G$2:$G$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"57*",'BALANCE N-1'!$H$2:$H$2000)))-((SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"592*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"593*",'BALANCE N-1'!$G$2:$G$2000)+SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$H$2:$H$2000)-SUMIF('BALANCE N-1'!$A$2:$A$2000,"595*",'BALANCE N-1'!$G$2:$G$2000)))</f>
         <v/>
       </c>
     </row>
